--- a/input/timetable/ИТиСС.xlsx
+++ b/input/timetable/ИТиСС.xlsx
@@ -197,9 +197,6 @@
     <t>Технологии сетей радиодоступа, п/г 1, У304//</t>
   </si>
   <si>
-    <t>Учебная практика, практика по получению первичных навыков научно-исследовательской работы, У306</t>
-  </si>
-  <si>
     <t>Электропитание устройств телекоммуникаций, п/г 1, А332//</t>
   </si>
   <si>
@@ -356,9 +353,6 @@
     <t>Безопасность жизнедеятельности (пр), А402//</t>
   </si>
   <si>
-    <t>Микропроцессорные устройства электросвязи (лек), У902</t>
-  </si>
-  <si>
     <t>Наземные и космические системы радиосвязи (лек), У304</t>
   </si>
   <si>
@@ -368,9 +362,6 @@
     <t>Информационная безопасность систем связи и телекоммуникаций (лек), ЭОиДОТ</t>
   </si>
   <si>
-    <t>Информационная безопасность систем связи и телекоммуникаций (пр), У304</t>
-  </si>
-  <si>
     <t>Планирование и управление сетями и системами связи (лек), ЭОиДОТ</t>
   </si>
   <si>
@@ -399,6 +390,15 @@
   </si>
   <si>
     <t>Физика (лек), А436</t>
+  </si>
+  <si>
+    <t>Микропроцессорные устройства электросвязи (лек), ЭОиДОТ</t>
+  </si>
+  <si>
+    <t>Учебная практика, практика по получению первичных навыков научно-исследовательской работы, ЭОиДОТ</t>
+  </si>
+  <si>
+    <t>Информационная безопасность систем связи и телекоммуникаций (пр), ЭОиДОТ</t>
   </si>
 </sst>
 </file>
@@ -1323,7 +1323,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="282">
+  <cellXfs count="276">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1496,6 +1496,84 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1533,15 +1611,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1593,74 +1662,66 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -1668,22 +1729,10 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1727,163 +1776,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1920,6 +1812,15 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1947,15 +1848,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1965,14 +1857,134 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -1996,47 +2008,17 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2372,7 +2354,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="64" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B2" s="65"/>
       <c r="C2" s="65"/>
@@ -2396,14 +2378,14 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="67" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
@@ -2411,7 +2393,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
@@ -2440,12 +2422,12 @@
       <c r="A7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="73" t="s">
+      <c r="C7" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="73"/>
+      <c r="D7" s="105"/>
       <c r="E7" s="46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>7</v>
@@ -2467,7 +2449,7 @@
         <v>33</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
@@ -2494,46 +2476,46 @@
       <c r="B11" s="25">
         <v>2</v>
       </c>
-      <c r="C11" s="101"/>
-      <c r="D11" s="102"/>
-      <c r="E11" s="102"/>
-      <c r="F11" s="103"/>
+      <c r="C11" s="130"/>
+      <c r="D11" s="131"/>
+      <c r="E11" s="131"/>
+      <c r="F11" s="132"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" s="26"/>
       <c r="B12" s="27">
         <v>3</v>
       </c>
-      <c r="C12" s="89" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" s="90"/>
-      <c r="E12" s="90"/>
-      <c r="F12" s="91"/>
+      <c r="C12" s="75" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="77"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" s="26"/>
       <c r="B13" s="27">
         <v>4</v>
       </c>
-      <c r="C13" s="83" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" s="84"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="85"/>
+      <c r="C13" s="115" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" s="116"/>
+      <c r="E13" s="116"/>
+      <c r="F13" s="117"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="28"/>
       <c r="B14" s="29">
         <v>6</v>
       </c>
-      <c r="C14" s="111" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" s="112"/>
-      <c r="E14" s="112"/>
-      <c r="F14" s="113"/>
+      <c r="C14" s="78" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="79"/>
+      <c r="E14" s="79"/>
+      <c r="F14" s="80"/>
     </row>
     <row r="15" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="30" t="s">
@@ -2542,46 +2524,46 @@
       <c r="B15" s="31">
         <v>1</v>
       </c>
-      <c r="C15" s="86" t="s">
-        <v>88</v>
-      </c>
-      <c r="D15" s="87"/>
-      <c r="E15" s="87"/>
-      <c r="F15" s="88"/>
+      <c r="C15" s="118" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" s="119"/>
+      <c r="E15" s="119"/>
+      <c r="F15" s="120"/>
     </row>
     <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="26"/>
       <c r="B16" s="27">
         <v>2</v>
       </c>
-      <c r="C16" s="80" t="s">
-        <v>125</v>
-      </c>
-      <c r="D16" s="81"/>
-      <c r="E16" s="81"/>
-      <c r="F16" s="82"/>
+      <c r="C16" s="112" t="s">
+        <v>122</v>
+      </c>
+      <c r="D16" s="113"/>
+      <c r="E16" s="113"/>
+      <c r="F16" s="114"/>
     </row>
     <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="26"/>
       <c r="B17" s="27">
         <v>3</v>
       </c>
-      <c r="C17" s="104"/>
-      <c r="D17" s="105"/>
-      <c r="E17" s="105"/>
-      <c r="F17" s="106"/>
+      <c r="C17" s="133"/>
+      <c r="D17" s="134"/>
+      <c r="E17" s="134"/>
+      <c r="F17" s="135"/>
     </row>
     <row r="18" spans="1:6" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="32"/>
       <c r="B18" s="29">
         <v>5</v>
       </c>
-      <c r="C18" s="92" t="s">
+      <c r="C18" s="121" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="93"/>
-      <c r="E18" s="93"/>
-      <c r="F18" s="94"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="123"/>
     </row>
     <row r="19" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="30" t="s">
@@ -2590,40 +2572,40 @@
       <c r="B19" s="31">
         <v>1</v>
       </c>
-      <c r="C19" s="98" t="s">
+      <c r="C19" s="127" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="99"/>
-      <c r="E19" s="99" t="s">
-        <v>94</v>
-      </c>
-      <c r="F19" s="100"/>
+      <c r="D19" s="128"/>
+      <c r="E19" s="128" t="s">
+        <v>93</v>
+      </c>
+      <c r="F19" s="129"/>
     </row>
     <row r="20" spans="1:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="26"/>
       <c r="B20" s="27">
         <v>2</v>
       </c>
-      <c r="C20" s="83" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" s="84"/>
-      <c r="E20" s="84" t="s">
-        <v>83</v>
-      </c>
-      <c r="F20" s="85"/>
+      <c r="C20" s="115" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" s="116"/>
+      <c r="E20" s="116" t="s">
+        <v>82</v>
+      </c>
+      <c r="F20" s="117"/>
     </row>
     <row r="21" spans="1:6" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="26"/>
       <c r="B21" s="27">
         <v>3</v>
       </c>
-      <c r="C21" s="107" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" s="108"/>
-      <c r="E21" s="109"/>
-      <c r="F21" s="110"/>
+      <c r="C21" s="136" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="137"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="74"/>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="30" t="s">
@@ -2632,44 +2614,44 @@
       <c r="B22" s="31">
         <v>1</v>
       </c>
-      <c r="C22" s="95" t="s">
-        <v>89</v>
-      </c>
-      <c r="D22" s="96"/>
-      <c r="E22" s="96"/>
-      <c r="F22" s="97"/>
+      <c r="C22" s="124" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" s="125"/>
+      <c r="E22" s="125"/>
+      <c r="F22" s="126"/>
     </row>
     <row r="23" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="26"/>
       <c r="B23" s="27">
         <v>2</v>
       </c>
-      <c r="C23" s="89" t="s">
-        <v>90</v>
-      </c>
-      <c r="D23" s="90"/>
-      <c r="E23" s="90"/>
-      <c r="F23" s="91"/>
+      <c r="C23" s="75" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23" s="76"/>
+      <c r="E23" s="76"/>
+      <c r="F23" s="77"/>
     </row>
     <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="26"/>
       <c r="B24" s="27">
         <v>3</v>
       </c>
-      <c r="C24" s="117"/>
-      <c r="D24" s="118"/>
-      <c r="E24" s="118"/>
-      <c r="F24" s="119"/>
+      <c r="C24" s="84"/>
+      <c r="D24" s="85"/>
+      <c r="E24" s="85"/>
+      <c r="F24" s="86"/>
     </row>
     <row r="25" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="32"/>
       <c r="B25" s="29">
         <v>4</v>
       </c>
-      <c r="C25" s="120"/>
-      <c r="D25" s="121"/>
-      <c r="E25" s="121"/>
-      <c r="F25" s="110"/>
+      <c r="C25" s="87"/>
+      <c r="D25" s="88"/>
+      <c r="E25" s="88"/>
+      <c r="F25" s="74"/>
     </row>
     <row r="26" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="30" t="s">
@@ -2678,46 +2660,46 @@
       <c r="B26" s="31">
         <v>1</v>
       </c>
-      <c r="C26" s="128"/>
-      <c r="D26" s="129"/>
-      <c r="E26" s="130" t="s">
-        <v>85</v>
-      </c>
-      <c r="F26" s="91"/>
+      <c r="C26" s="95"/>
+      <c r="D26" s="96"/>
+      <c r="E26" s="97" t="s">
+        <v>84</v>
+      </c>
+      <c r="F26" s="77"/>
     </row>
     <row r="27" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="33"/>
       <c r="B27" s="27">
         <v>2</v>
       </c>
-      <c r="C27" s="89" t="s">
+      <c r="C27" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="D27" s="90"/>
-      <c r="E27" s="90"/>
-      <c r="F27" s="91"/>
+      <c r="D27" s="76"/>
+      <c r="E27" s="76"/>
+      <c r="F27" s="77"/>
     </row>
     <row r="28" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="33"/>
       <c r="B28" s="27">
         <v>3</v>
       </c>
-      <c r="C28" s="125" t="s">
+      <c r="C28" s="92" t="s">
         <v>28</v>
       </c>
-      <c r="D28" s="126"/>
-      <c r="E28" s="126"/>
-      <c r="F28" s="127"/>
+      <c r="D28" s="93"/>
+      <c r="E28" s="93"/>
+      <c r="F28" s="94"/>
     </row>
     <row r="29" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="34"/>
       <c r="B29" s="29">
         <v>4</v>
       </c>
-      <c r="C29" s="74"/>
-      <c r="D29" s="75"/>
-      <c r="E29" s="75"/>
-      <c r="F29" s="76"/>
+      <c r="C29" s="106"/>
+      <c r="D29" s="107"/>
+      <c r="E29" s="107"/>
+      <c r="F29" s="108"/>
     </row>
     <row r="30" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="35" t="s">
@@ -2726,76 +2708,76 @@
       <c r="B30" s="25">
         <v>2</v>
       </c>
-      <c r="C30" s="122"/>
-      <c r="D30" s="123"/>
-      <c r="E30" s="123"/>
-      <c r="F30" s="124"/>
+      <c r="C30" s="89"/>
+      <c r="D30" s="90"/>
+      <c r="E30" s="90"/>
+      <c r="F30" s="91"/>
     </row>
     <row r="31" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="36"/>
       <c r="B31" s="25">
         <v>3</v>
       </c>
-      <c r="C31" s="134" t="s">
+      <c r="C31" s="101" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" s="102"/>
+      <c r="E31" s="103" t="s">
         <v>81</v>
       </c>
-      <c r="D31" s="135"/>
-      <c r="E31" s="136" t="s">
-        <v>82</v>
-      </c>
-      <c r="F31" s="137"/>
+      <c r="F31" s="104"/>
     </row>
     <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="36"/>
       <c r="B32" s="25">
         <v>4</v>
       </c>
-      <c r="C32" s="117"/>
-      <c r="D32" s="118"/>
-      <c r="E32" s="118"/>
-      <c r="F32" s="119"/>
+      <c r="C32" s="84"/>
+      <c r="D32" s="85"/>
+      <c r="E32" s="85"/>
+      <c r="F32" s="86"/>
     </row>
     <row r="33" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="36"/>
       <c r="B33" s="37">
         <v>5</v>
       </c>
-      <c r="C33" s="120"/>
-      <c r="D33" s="121"/>
-      <c r="E33" s="121"/>
-      <c r="F33" s="110"/>
+      <c r="C33" s="87"/>
+      <c r="D33" s="88"/>
+      <c r="E33" s="88"/>
+      <c r="F33" s="74"/>
     </row>
     <row r="34" spans="1:6" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="38"/>
       <c r="B34" s="39"/>
-      <c r="C34" s="77"/>
-      <c r="D34" s="78"/>
-      <c r="E34" s="78"/>
-      <c r="F34" s="79"/>
+      <c r="C34" s="109"/>
+      <c r="D34" s="110"/>
+      <c r="E34" s="110"/>
+      <c r="F34" s="111"/>
     </row>
     <row r="35" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="68"/>
       <c r="B35" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="131" t="s">
-        <v>79</v>
-      </c>
-      <c r="D35" s="132"/>
-      <c r="E35" s="132"/>
-      <c r="F35" s="133"/>
+      <c r="C35" s="98" t="s">
+        <v>78</v>
+      </c>
+      <c r="D35" s="99"/>
+      <c r="E35" s="99"/>
+      <c r="F35" s="100"/>
     </row>
     <row r="36" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="45"/>
       <c r="B36" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="C36" s="114" t="s">
+      <c r="C36" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="115"/>
-      <c r="E36" s="115"/>
-      <c r="F36" s="116"/>
+      <c r="D36" s="82"/>
+      <c r="E36" s="82"/>
+      <c r="F36" s="83"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
@@ -2815,6 +2797,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="E21:F21"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C14:F14"/>
@@ -2831,22 +2829,6 @@
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="E31:F31"/>
     <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="C21:D21"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:E9">
     <cfRule type="expression" priority="2">
@@ -2900,7 +2882,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="64" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B2" s="65"/>
       <c r="C2" s="65"/>
@@ -2931,7 +2913,7 @@
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="67" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
@@ -2939,7 +2921,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
@@ -2968,10 +2950,10 @@
       <c r="A7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="73" t="s">
+      <c r="C7" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="73"/>
+      <c r="D7" s="105"/>
       <c r="E7" s="46" t="s">
         <v>40</v>
       </c>
@@ -2994,10 +2976,10 @@
       <c r="A9" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="172" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" s="172"/>
+      <c r="C9" s="143" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="143"/>
       <c r="E9" s="17"/>
       <c r="F9" s="16"/>
     </row>
@@ -3022,48 +3004,48 @@
       <c r="B11" s="31">
         <v>1</v>
       </c>
-      <c r="C11" s="173" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" s="174"/>
-      <c r="E11" s="174"/>
-      <c r="F11" s="175"/>
+      <c r="C11" s="144" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" s="145"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="146"/>
     </row>
     <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="26"/>
       <c r="B12" s="27">
         <v>2</v>
       </c>
-      <c r="C12" s="134" t="s">
+      <c r="C12" s="101" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="176"/>
-      <c r="E12" s="176"/>
-      <c r="F12" s="137"/>
+      <c r="D12" s="147"/>
+      <c r="E12" s="147"/>
+      <c r="F12" s="104"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" s="26"/>
       <c r="B13" s="27">
         <v>3</v>
       </c>
-      <c r="C13" s="134" t="s">
+      <c r="C13" s="101" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="176"/>
-      <c r="E13" s="176"/>
-      <c r="F13" s="137"/>
+      <c r="D13" s="147"/>
+      <c r="E13" s="147"/>
+      <c r="F13" s="104"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="26"/>
       <c r="B14" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="177" t="s">
+      <c r="C14" s="148" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="178"/>
-      <c r="E14" s="178"/>
-      <c r="F14" s="179"/>
+      <c r="D14" s="149"/>
+      <c r="E14" s="149"/>
+      <c r="F14" s="150"/>
     </row>
     <row r="15" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="30" t="s">
@@ -3072,52 +3054,52 @@
       <c r="B15" s="31">
         <v>2</v>
       </c>
-      <c r="C15" s="98" t="s">
+      <c r="C15" s="127" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="99"/>
-      <c r="E15" s="99"/>
-      <c r="F15" s="100"/>
+      <c r="D15" s="128"/>
+      <c r="E15" s="128"/>
+      <c r="F15" s="129"/>
     </row>
     <row r="16" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="26"/>
       <c r="B16" s="27">
         <v>3</v>
       </c>
-      <c r="C16" s="185" t="s">
+      <c r="C16" s="156" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="186"/>
-      <c r="E16" s="186"/>
-      <c r="F16" s="187"/>
+      <c r="D16" s="157"/>
+      <c r="E16" s="157"/>
+      <c r="F16" s="158"/>
     </row>
     <row r="17" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="26"/>
       <c r="B17" s="27">
         <v>4</v>
       </c>
-      <c r="C17" s="80" t="s">
+      <c r="C17" s="112" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="81"/>
-      <c r="E17" s="81" t="s">
-        <v>97</v>
-      </c>
-      <c r="F17" s="82"/>
+      <c r="D17" s="113"/>
+      <c r="E17" s="113" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" s="114"/>
     </row>
     <row r="18" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="32"/>
       <c r="B18" s="29">
         <v>5</v>
       </c>
-      <c r="C18" s="92" t="s">
+      <c r="C18" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="183"/>
-      <c r="E18" s="184" t="s">
-        <v>68</v>
-      </c>
-      <c r="F18" s="94"/>
+      <c r="D18" s="154"/>
+      <c r="E18" s="155" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="123"/>
     </row>
     <row r="19" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="30" t="s">
@@ -3126,50 +3108,50 @@
       <c r="B19" s="31">
         <v>1</v>
       </c>
-      <c r="C19" s="180"/>
-      <c r="D19" s="181"/>
-      <c r="E19" s="181"/>
-      <c r="F19" s="182"/>
+      <c r="C19" s="151"/>
+      <c r="D19" s="152"/>
+      <c r="E19" s="152"/>
+      <c r="F19" s="153"/>
     </row>
     <row r="20" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="26"/>
       <c r="B20" s="27">
         <v>2</v>
       </c>
-      <c r="C20" s="171" t="s">
+      <c r="C20" s="141" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="144"/>
-      <c r="E20" s="144" t="s">
+      <c r="D20" s="142"/>
+      <c r="E20" s="142" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="145"/>
+      <c r="F20" s="165"/>
     </row>
     <row r="21" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="26"/>
       <c r="B21" s="27">
         <v>3</v>
       </c>
-      <c r="C21" s="83" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" s="84"/>
-      <c r="E21" s="84" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21" s="85"/>
+      <c r="C21" s="115" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="116"/>
+      <c r="E21" s="116" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="117"/>
     </row>
     <row r="22" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="32"/>
       <c r="B22" s="29">
         <v>4</v>
       </c>
-      <c r="C22" s="150" t="s">
-        <v>99</v>
-      </c>
-      <c r="D22" s="151"/>
-      <c r="E22" s="151"/>
-      <c r="F22" s="152"/>
+      <c r="C22" s="167" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" s="168"/>
+      <c r="E22" s="168"/>
+      <c r="F22" s="169"/>
     </row>
     <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="30" t="s">
@@ -3178,46 +3160,46 @@
       <c r="B23" s="31">
         <v>1</v>
       </c>
-      <c r="C23" s="147"/>
-      <c r="D23" s="148"/>
-      <c r="E23" s="148"/>
-      <c r="F23" s="149"/>
+      <c r="C23" s="138"/>
+      <c r="D23" s="139"/>
+      <c r="E23" s="139"/>
+      <c r="F23" s="140"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" s="26"/>
       <c r="B24" s="27">
         <v>2</v>
       </c>
-      <c r="C24" s="89" t="s">
-        <v>100</v>
-      </c>
-      <c r="D24" s="90"/>
-      <c r="E24" s="90"/>
-      <c r="F24" s="91"/>
+      <c r="C24" s="75" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="76"/>
+      <c r="E24" s="76"/>
+      <c r="F24" s="77"/>
     </row>
     <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="26"/>
       <c r="B25" s="27">
         <v>3</v>
       </c>
-      <c r="C25" s="89" t="s">
-        <v>110</v>
-      </c>
-      <c r="D25" s="90"/>
-      <c r="E25" s="90"/>
-      <c r="F25" s="91"/>
+      <c r="C25" s="75" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" s="76"/>
+      <c r="E25" s="76"/>
+      <c r="F25" s="77"/>
     </row>
     <row r="26" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="32"/>
       <c r="B26" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="153" t="s">
+      <c r="C26" s="170" t="s">
         <v>43</v>
       </c>
-      <c r="D26" s="154"/>
-      <c r="E26" s="154"/>
-      <c r="F26" s="155"/>
+      <c r="D26" s="171"/>
+      <c r="E26" s="171"/>
+      <c r="F26" s="172"/>
     </row>
     <row r="27" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="30" t="s">
@@ -3226,44 +3208,44 @@
       <c r="B27" s="31">
         <v>2</v>
       </c>
-      <c r="C27" s="147"/>
-      <c r="D27" s="148"/>
-      <c r="E27" s="148"/>
-      <c r="F27" s="149"/>
+      <c r="C27" s="138"/>
+      <c r="D27" s="139"/>
+      <c r="E27" s="139"/>
+      <c r="F27" s="140"/>
     </row>
     <row r="28" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="33"/>
       <c r="B28" s="27">
         <v>3</v>
       </c>
-      <c r="C28" s="117"/>
-      <c r="D28" s="118"/>
-      <c r="E28" s="118"/>
-      <c r="F28" s="119"/>
+      <c r="C28" s="84"/>
+      <c r="D28" s="85"/>
+      <c r="E28" s="85"/>
+      <c r="F28" s="86"/>
     </row>
     <row r="29" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="33"/>
       <c r="B29" s="27">
         <v>4</v>
       </c>
-      <c r="C29" s="165" t="s">
+      <c r="C29" s="182" t="s">
         <v>35</v>
       </c>
-      <c r="D29" s="166"/>
-      <c r="E29" s="166"/>
-      <c r="F29" s="167"/>
+      <c r="D29" s="183"/>
+      <c r="E29" s="183"/>
+      <c r="F29" s="184"/>
     </row>
     <row r="30" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="34"/>
       <c r="B30" s="29">
         <v>5</v>
       </c>
-      <c r="C30" s="168" t="s">
-        <v>101</v>
-      </c>
-      <c r="D30" s="169"/>
-      <c r="E30" s="169"/>
-      <c r="F30" s="170"/>
+      <c r="C30" s="185" t="s">
+        <v>100</v>
+      </c>
+      <c r="D30" s="186"/>
+      <c r="E30" s="186"/>
+      <c r="F30" s="187"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="50" t="s">
@@ -3272,87 +3254,87 @@
       <c r="B31" s="31">
         <v>2</v>
       </c>
-      <c r="C31" s="141" t="s">
+      <c r="C31" s="162" t="s">
         <v>37</v>
       </c>
-      <c r="D31" s="142"/>
-      <c r="E31" s="142"/>
-      <c r="F31" s="143"/>
+      <c r="D31" s="163"/>
+      <c r="E31" s="163"/>
+      <c r="F31" s="164"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B32" s="62">
         <v>3</v>
       </c>
-      <c r="C32" s="138"/>
-      <c r="D32" s="139"/>
-      <c r="E32" s="139"/>
-      <c r="F32" s="140"/>
+      <c r="C32" s="159"/>
+      <c r="D32" s="160"/>
+      <c r="E32" s="160"/>
+      <c r="F32" s="161"/>
     </row>
     <row r="33" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="45"/>
       <c r="B33" s="29">
         <v>4</v>
       </c>
-      <c r="C33" s="120"/>
-      <c r="D33" s="121"/>
-      <c r="E33" s="121"/>
-      <c r="F33" s="110"/>
+      <c r="C33" s="87"/>
+      <c r="D33" s="88"/>
+      <c r="E33" s="88"/>
+      <c r="F33" s="74"/>
     </row>
     <row r="34" spans="1:6" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="55"/>
       <c r="B34" s="56"/>
-      <c r="C34" s="161"/>
-      <c r="D34" s="161"/>
-      <c r="E34" s="161"/>
-      <c r="F34" s="161"/>
+      <c r="C34" s="178"/>
+      <c r="D34" s="178"/>
+      <c r="E34" s="178"/>
+      <c r="F34" s="178"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" s="53"/>
       <c r="B35" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="158" t="s">
-        <v>91</v>
-      </c>
-      <c r="D35" s="159"/>
-      <c r="E35" s="159"/>
-      <c r="F35" s="160"/>
+      <c r="C35" s="175" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35" s="176"/>
+      <c r="E35" s="176"/>
+      <c r="F35" s="177"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" s="71"/>
       <c r="B36" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="C36" s="162" t="s">
-        <v>93</v>
-      </c>
-      <c r="D36" s="163"/>
-      <c r="E36" s="163"/>
-      <c r="F36" s="164"/>
+      <c r="C36" s="179" t="s">
+        <v>92</v>
+      </c>
+      <c r="D36" s="180"/>
+      <c r="E36" s="180"/>
+      <c r="F36" s="181"/>
     </row>
     <row r="37" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="54"/>
       <c r="B37" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="156" t="s">
-        <v>92</v>
-      </c>
-      <c r="D37" s="115"/>
-      <c r="E37" s="115"/>
-      <c r="F37" s="157"/>
+      <c r="C37" s="173" t="s">
+        <v>91</v>
+      </c>
+      <c r="D37" s="82"/>
+      <c r="E37" s="82"/>
+      <c r="F37" s="174"/>
     </row>
     <row r="38" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="60" t="s">
         <v>44</v>
       </c>
       <c r="B38" s="61"/>
-      <c r="C38" s="146" t="s">
+      <c r="C38" s="166" t="s">
         <v>49</v>
       </c>
-      <c r="D38" s="146"/>
-      <c r="E38" s="146"/>
-      <c r="F38" s="146"/>
+      <c r="D38" s="166"/>
+      <c r="E38" s="166"/>
+      <c r="F38" s="166"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
@@ -3372,8 +3354,24 @@
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C20:D20"/>
@@ -3390,22 +3388,6 @@
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="E18:F18"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:E9">
     <cfRule type="expression" priority="3">
@@ -3460,7 +3442,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
@@ -3483,7 +3465,7 @@
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.4">
@@ -3491,7 +3473,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
@@ -3520,10 +3502,10 @@
       <c r="A7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="73" t="s">
+      <c r="C7" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="73"/>
+      <c r="D7" s="105"/>
       <c r="E7" s="46" t="s">
         <v>38</v>
       </c>
@@ -3535,12 +3517,12 @@
       <c r="A8" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="239" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" s="239"/>
-      <c r="E8" s="239"/>
-      <c r="F8" s="239"/>
+      <c r="C8" s="203" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="203"/>
+      <c r="E8" s="203"/>
+      <c r="F8" s="203"/>
     </row>
     <row r="9" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="18" t="s">
@@ -3560,24 +3542,24 @@
       <c r="A10" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="25">
-        <v>2</v>
-      </c>
-      <c r="C10" s="230" t="s">
-        <v>111</v>
-      </c>
-      <c r="D10" s="231"/>
-      <c r="E10" s="231"/>
-      <c r="F10" s="232"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="194"/>
+      <c r="D10" s="195"/>
+      <c r="E10" s="195"/>
+      <c r="F10" s="196"/>
       <c r="K10" s="63"/>
     </row>
     <row r="11" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="26"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="249"/>
-      <c r="D11" s="250"/>
-      <c r="E11" s="250"/>
-      <c r="F11" s="251"/>
+      <c r="B11" s="25">
+        <v>4</v>
+      </c>
+      <c r="C11" s="204" t="s">
+        <v>123</v>
+      </c>
+      <c r="D11" s="205"/>
+      <c r="E11" s="205"/>
+      <c r="F11" s="206"/>
       <c r="K11" s="63"/>
     </row>
     <row r="12" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -3585,24 +3567,24 @@
       <c r="B12" s="27">
         <v>5</v>
       </c>
-      <c r="C12" s="243" t="s">
-        <v>102</v>
-      </c>
-      <c r="D12" s="244"/>
-      <c r="E12" s="244"/>
-      <c r="F12" s="245"/>
+      <c r="C12" s="210" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" s="211"/>
+      <c r="E12" s="211"/>
+      <c r="F12" s="212"/>
     </row>
     <row r="13" spans="1:11" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="28"/>
       <c r="B13" s="29">
         <v>6</v>
       </c>
-      <c r="C13" s="246" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="247"/>
-      <c r="E13" s="247"/>
-      <c r="F13" s="248"/>
+      <c r="C13" s="213" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="214"/>
+      <c r="E13" s="214"/>
+      <c r="F13" s="215"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="30" t="s">
@@ -3611,50 +3593,50 @@
       <c r="B14" s="31">
         <v>1</v>
       </c>
-      <c r="C14" s="233" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" s="234"/>
-      <c r="E14" s="234"/>
-      <c r="F14" s="235"/>
+      <c r="C14" s="197" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="198"/>
+      <c r="E14" s="198"/>
+      <c r="F14" s="199"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="26"/>
       <c r="B15" s="25">
         <v>2</v>
       </c>
-      <c r="C15" s="224" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" s="225"/>
-      <c r="E15" s="225"/>
-      <c r="F15" s="226"/>
+      <c r="C15" s="188" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" s="189"/>
+      <c r="E15" s="189"/>
+      <c r="F15" s="190"/>
     </row>
     <row r="16" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="26"/>
       <c r="B16" s="27">
         <v>3</v>
       </c>
-      <c r="C16" s="191" t="s">
+      <c r="C16" s="238" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="239"/>
+      <c r="E16" s="240" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="192"/>
-      <c r="E16" s="193" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16" s="194"/>
+      <c r="F16" s="241"/>
     </row>
     <row r="17" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="32"/>
       <c r="B17" s="29">
         <v>4</v>
       </c>
-      <c r="C17" s="236" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17" s="237"/>
-      <c r="E17" s="237"/>
-      <c r="F17" s="238"/>
+      <c r="C17" s="200" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="201"/>
+      <c r="E17" s="201"/>
+      <c r="F17" s="202"/>
     </row>
     <row r="18" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="30" t="s">
@@ -3663,48 +3645,46 @@
       <c r="B18" s="31">
         <v>3</v>
       </c>
-      <c r="C18" s="252" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" s="253"/>
-      <c r="E18" s="253" t="s">
-        <v>109</v>
-      </c>
-      <c r="F18" s="254"/>
-    </row>
-    <row r="19" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C18" s="216" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="217"/>
+      <c r="E18" s="217" t="s">
+        <v>108</v>
+      </c>
+      <c r="F18" s="218"/>
+    </row>
+    <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="26"/>
       <c r="B19" s="27">
         <v>4</v>
       </c>
-      <c r="C19" s="208" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="209"/>
-      <c r="E19" s="209"/>
-      <c r="F19" s="210"/>
+      <c r="C19" s="204" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="205"/>
+      <c r="E19" s="205"/>
+      <c r="F19" s="206"/>
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="26"/>
       <c r="B20" s="27">
         <v>5</v>
       </c>
-      <c r="C20" s="208" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="209"/>
-      <c r="E20" s="209"/>
-      <c r="F20" s="210"/>
+      <c r="C20" s="204"/>
+      <c r="D20" s="205"/>
+      <c r="E20" s="205"/>
+      <c r="F20" s="206"/>
     </row>
     <row r="21" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="32"/>
       <c r="B21" s="29">
         <v>6</v>
       </c>
-      <c r="C21" s="240"/>
-      <c r="D21" s="241"/>
-      <c r="E21" s="241"/>
-      <c r="F21" s="242"/>
+      <c r="C21" s="207"/>
+      <c r="D21" s="208"/>
+      <c r="E21" s="208"/>
+      <c r="F21" s="209"/>
     </row>
     <row r="22" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="30" t="s">
@@ -3713,44 +3693,46 @@
       <c r="B22" s="31">
         <v>3</v>
       </c>
-      <c r="C22" s="198"/>
-      <c r="D22" s="199"/>
-      <c r="E22" s="199"/>
-      <c r="F22" s="200"/>
+      <c r="C22" s="242"/>
+      <c r="D22" s="243"/>
+      <c r="E22" s="243"/>
+      <c r="F22" s="244"/>
     </row>
     <row r="23" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="26"/>
       <c r="B23" s="27">
         <v>4</v>
       </c>
-      <c r="C23" s="201" t="s">
-        <v>106</v>
-      </c>
-      <c r="D23" s="202"/>
-      <c r="E23" s="203"/>
-      <c r="F23" s="204"/>
+      <c r="C23" s="245" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" s="246"/>
+      <c r="E23" s="247"/>
+      <c r="F23" s="248"/>
     </row>
     <row r="24" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="26"/>
       <c r="B24" s="27">
         <v>5</v>
       </c>
-      <c r="C24" s="201"/>
-      <c r="D24" s="202"/>
-      <c r="E24" s="203" t="s">
-        <v>124</v>
-      </c>
-      <c r="F24" s="204"/>
-    </row>
-    <row r="25" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C24" s="245"/>
+      <c r="D24" s="246"/>
+      <c r="E24" s="247" t="s">
+        <v>121</v>
+      </c>
+      <c r="F24" s="248"/>
+    </row>
+    <row r="25" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="32"/>
       <c r="B25" s="29">
         <v>6</v>
       </c>
-      <c r="C25" s="195"/>
-      <c r="D25" s="196"/>
-      <c r="E25" s="196"/>
-      <c r="F25" s="197"/>
+      <c r="C25" s="207" t="s">
+        <v>124</v>
+      </c>
+      <c r="D25" s="208"/>
+      <c r="E25" s="208"/>
+      <c r="F25" s="209"/>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="30" t="s">
@@ -3759,48 +3741,48 @@
       <c r="B26" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="227" t="s">
+      <c r="C26" s="191" t="s">
         <v>43</v>
       </c>
-      <c r="D26" s="228"/>
-      <c r="E26" s="228"/>
-      <c r="F26" s="229"/>
+      <c r="D26" s="192"/>
+      <c r="E26" s="192"/>
+      <c r="F26" s="193"/>
     </row>
     <row r="27" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="33"/>
       <c r="B27" s="27">
         <v>4</v>
       </c>
-      <c r="C27" s="188" t="s">
-        <v>104</v>
-      </c>
-      <c r="D27" s="189"/>
-      <c r="E27" s="189"/>
-      <c r="F27" s="190"/>
+      <c r="C27" s="235" t="s">
+        <v>103</v>
+      </c>
+      <c r="D27" s="236"/>
+      <c r="E27" s="236"/>
+      <c r="F27" s="237"/>
     </row>
     <row r="28" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="33"/>
       <c r="B28" s="27">
         <v>5</v>
       </c>
-      <c r="C28" s="208" t="s">
-        <v>105</v>
-      </c>
-      <c r="D28" s="209"/>
-      <c r="E28" s="209"/>
-      <c r="F28" s="210"/>
+      <c r="C28" s="204" t="s">
+        <v>104</v>
+      </c>
+      <c r="D28" s="205"/>
+      <c r="E28" s="205"/>
+      <c r="F28" s="206"/>
     </row>
     <row r="29" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="34"/>
       <c r="B29" s="29">
         <v>6</v>
       </c>
-      <c r="C29" s="220" t="s">
+      <c r="C29" s="231" t="s">
         <v>57</v>
       </c>
-      <c r="D29" s="221"/>
-      <c r="E29" s="222"/>
-      <c r="F29" s="223"/>
+      <c r="D29" s="232"/>
+      <c r="E29" s="233"/>
+      <c r="F29" s="234"/>
     </row>
     <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="50" t="s">
@@ -3809,76 +3791,76 @@
       <c r="B30" s="31">
         <v>1</v>
       </c>
-      <c r="C30" s="205"/>
-      <c r="D30" s="206"/>
-      <c r="E30" s="206"/>
-      <c r="F30" s="207"/>
+      <c r="C30" s="219"/>
+      <c r="D30" s="220"/>
+      <c r="E30" s="220"/>
+      <c r="F30" s="221"/>
     </row>
     <row r="31" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="47"/>
       <c r="B31" s="27">
         <v>2</v>
       </c>
-      <c r="C31" s="208" t="s">
-        <v>107</v>
-      </c>
-      <c r="D31" s="209"/>
-      <c r="E31" s="209"/>
-      <c r="F31" s="210"/>
+      <c r="C31" s="204" t="s">
+        <v>106</v>
+      </c>
+      <c r="D31" s="205"/>
+      <c r="E31" s="205"/>
+      <c r="F31" s="206"/>
     </row>
     <row r="32" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="47"/>
       <c r="B32" s="27">
         <v>3</v>
       </c>
-      <c r="C32" s="208" t="s">
-        <v>108</v>
-      </c>
-      <c r="D32" s="209"/>
-      <c r="E32" s="209"/>
-      <c r="F32" s="210"/>
+      <c r="C32" s="204" t="s">
+        <v>107</v>
+      </c>
+      <c r="D32" s="205"/>
+      <c r="E32" s="205"/>
+      <c r="F32" s="206"/>
     </row>
     <row r="33" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="45"/>
       <c r="B33" s="29">
         <v>4</v>
       </c>
-      <c r="C33" s="217"/>
-      <c r="D33" s="218"/>
-      <c r="E33" s="218"/>
-      <c r="F33" s="219"/>
+      <c r="C33" s="228"/>
+      <c r="D33" s="229"/>
+      <c r="E33" s="229"/>
+      <c r="F33" s="230"/>
     </row>
     <row r="34" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="57"/>
       <c r="B34" s="58"/>
-      <c r="C34" s="211"/>
-      <c r="D34" s="212"/>
-      <c r="E34" s="212"/>
-      <c r="F34" s="213"/>
+      <c r="C34" s="222"/>
+      <c r="D34" s="223"/>
+      <c r="E34" s="223"/>
+      <c r="F34" s="224"/>
     </row>
     <row r="35" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="40"/>
       <c r="B35" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="214" t="s">
+      <c r="C35" s="225" t="s">
         <v>56</v>
       </c>
-      <c r="D35" s="215"/>
-      <c r="E35" s="215"/>
-      <c r="F35" s="216"/>
+      <c r="D35" s="226"/>
+      <c r="E35" s="226"/>
+      <c r="F35" s="227"/>
     </row>
     <row r="36" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="60" t="s">
         <v>44</v>
       </c>
       <c r="B36" s="61"/>
-      <c r="C36" s="146" t="s">
+      <c r="C36" s="166" t="s">
         <v>45</v>
       </c>
-      <c r="D36" s="146"/>
-      <c r="E36" s="146"/>
-      <c r="F36" s="146"/>
+      <c r="D36" s="166"/>
+      <c r="E36" s="166"/>
+      <c r="F36" s="166"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
@@ -3898,6 +3880,25 @@
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C32:F32"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C26:F26"/>
@@ -3913,25 +3914,6 @@
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="E18:F18"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E24:F24"/>
   </mergeCells>
   <conditionalFormatting sqref="C8">
     <cfRule type="expression" priority="1">
@@ -3980,7 +3962,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="64" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B2" s="65"/>
       <c r="C2" s="65"/>
@@ -4004,14 +3986,14 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="67" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
@@ -4019,7 +4001,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
@@ -4048,10 +4030,10 @@
       <c r="A7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="270" t="s">
+      <c r="C7" s="249" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="270"/>
+      <c r="D7" s="249"/>
       <c r="E7" s="46" t="s">
         <v>29</v>
       </c>
@@ -4063,12 +4045,12 @@
       <c r="A8" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="239" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" s="239"/>
-      <c r="E8" s="239"/>
-      <c r="F8" s="239"/>
+      <c r="C8" s="203" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="203"/>
+      <c r="E8" s="203"/>
+      <c r="F8" s="203"/>
     </row>
     <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="18" t="s">
@@ -4091,94 +4073,94 @@
       <c r="B10" s="25">
         <v>2</v>
       </c>
-      <c r="C10" s="274"/>
-      <c r="D10" s="275"/>
-      <c r="E10" s="275"/>
-      <c r="F10" s="276"/>
+      <c r="C10" s="253"/>
+      <c r="D10" s="254"/>
+      <c r="E10" s="254"/>
+      <c r="F10" s="255"/>
     </row>
     <row r="11" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="26"/>
       <c r="B11" s="27">
         <v>3</v>
       </c>
-      <c r="C11" s="134" t="s">
-        <v>119</v>
-      </c>
-      <c r="D11" s="176"/>
-      <c r="E11" s="176"/>
-      <c r="F11" s="137"/>
+      <c r="C11" s="101" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" s="147"/>
+      <c r="E11" s="147"/>
+      <c r="F11" s="104"/>
     </row>
     <row r="12" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="26"/>
       <c r="B12" s="27">
         <v>4</v>
       </c>
-      <c r="C12" s="171" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" s="144"/>
-      <c r="E12" s="144"/>
-      <c r="F12" s="145"/>
-    </row>
-    <row r="13" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C12" s="141" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" s="142"/>
+      <c r="E12" s="142"/>
+      <c r="F12" s="165"/>
+    </row>
+    <row r="13" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="28"/>
       <c r="B13" s="29">
         <v>5</v>
       </c>
-      <c r="C13" s="279" t="s">
-        <v>113</v>
-      </c>
-      <c r="D13" s="280"/>
-      <c r="E13" s="280"/>
-      <c r="F13" s="281"/>
+      <c r="C13" s="259" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13" s="260"/>
+      <c r="E13" s="260"/>
+      <c r="F13" s="261"/>
     </row>
     <row r="14" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="30" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="31">
-        <v>2</v>
-      </c>
-      <c r="C14" s="271"/>
-      <c r="D14" s="272"/>
-      <c r="E14" s="272"/>
-      <c r="F14" s="273"/>
+        <v>3</v>
+      </c>
+      <c r="C14" s="250"/>
+      <c r="D14" s="251"/>
+      <c r="E14" s="251"/>
+      <c r="F14" s="252"/>
     </row>
     <row r="15" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="26"/>
       <c r="B15" s="27">
-        <v>3</v>
-      </c>
-      <c r="C15" s="89" t="s">
-        <v>114</v>
-      </c>
-      <c r="D15" s="90"/>
-      <c r="E15" s="90"/>
-      <c r="F15" s="91"/>
-    </row>
-    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>4</v>
+      </c>
+      <c r="C15" s="75" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15" s="76"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="77"/>
+    </row>
+    <row r="16" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="26"/>
       <c r="B16" s="27">
         <v>5</v>
       </c>
-      <c r="C16" s="134" t="s">
-        <v>115</v>
-      </c>
-      <c r="D16" s="176"/>
-      <c r="E16" s="176"/>
-      <c r="F16" s="137"/>
-    </row>
-    <row r="17" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C16" s="101" t="s">
+        <v>125</v>
+      </c>
+      <c r="D16" s="147"/>
+      <c r="E16" s="147"/>
+      <c r="F16" s="104"/>
+    </row>
+    <row r="17" spans="1:6" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="32"/>
       <c r="B17" s="29">
         <v>6</v>
       </c>
-      <c r="C17" s="153" t="s">
-        <v>115</v>
-      </c>
-      <c r="D17" s="154"/>
-      <c r="E17" s="154"/>
-      <c r="F17" s="155"/>
+      <c r="C17" s="170" t="s">
+        <v>125</v>
+      </c>
+      <c r="D17" s="171"/>
+      <c r="E17" s="171"/>
+      <c r="F17" s="172"/>
     </row>
     <row r="18" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="30" t="s">
@@ -4187,48 +4169,48 @@
       <c r="B18" s="31">
         <v>2</v>
       </c>
-      <c r="C18" s="277" t="s">
-        <v>118</v>
-      </c>
-      <c r="D18" s="278"/>
-      <c r="E18" s="278"/>
-      <c r="F18" s="268"/>
+      <c r="C18" s="256" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18" s="257"/>
+      <c r="E18" s="257"/>
+      <c r="F18" s="258"/>
     </row>
     <row r="19" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="26"/>
       <c r="B19" s="27">
         <v>3</v>
       </c>
-      <c r="C19" s="185" t="s">
-        <v>118</v>
-      </c>
-      <c r="D19" s="186"/>
-      <c r="E19" s="186"/>
-      <c r="F19" s="187"/>
+      <c r="C19" s="156" t="s">
+        <v>115</v>
+      </c>
+      <c r="D19" s="157"/>
+      <c r="E19" s="157"/>
+      <c r="F19" s="158"/>
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="26"/>
       <c r="B20" s="27">
         <v>5</v>
       </c>
-      <c r="C20" s="134" t="s">
-        <v>116</v>
-      </c>
-      <c r="D20" s="176"/>
-      <c r="E20" s="176"/>
-      <c r="F20" s="137"/>
+      <c r="C20" s="101" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20" s="147"/>
+      <c r="E20" s="147"/>
+      <c r="F20" s="104"/>
     </row>
     <row r="21" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="32"/>
       <c r="B21" s="29">
         <v>6</v>
       </c>
-      <c r="C21" s="177" t="s">
-        <v>117</v>
-      </c>
-      <c r="D21" s="178"/>
-      <c r="E21" s="178"/>
-      <c r="F21" s="179"/>
+      <c r="C21" s="148" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" s="149"/>
+      <c r="E21" s="149"/>
+      <c r="F21" s="150"/>
     </row>
     <row r="22" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="30" t="s">
@@ -4237,44 +4219,44 @@
       <c r="B22" s="31">
         <v>3</v>
       </c>
-      <c r="C22" s="271"/>
-      <c r="D22" s="272"/>
-      <c r="E22" s="272"/>
-      <c r="F22" s="273"/>
+      <c r="C22" s="250"/>
+      <c r="D22" s="251"/>
+      <c r="E22" s="251"/>
+      <c r="F22" s="252"/>
     </row>
     <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="26"/>
       <c r="B23" s="27">
         <v>4</v>
       </c>
-      <c r="C23" s="117"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="118"/>
-      <c r="F23" s="119"/>
+      <c r="C23" s="84"/>
+      <c r="D23" s="85"/>
+      <c r="E23" s="85"/>
+      <c r="F23" s="86"/>
     </row>
     <row r="24" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="26"/>
       <c r="B24" s="27">
         <v>5</v>
       </c>
-      <c r="C24" s="134" t="s">
-        <v>116</v>
-      </c>
-      <c r="D24" s="176"/>
-      <c r="E24" s="176"/>
-      <c r="F24" s="137"/>
+      <c r="C24" s="101" t="s">
+        <v>113</v>
+      </c>
+      <c r="D24" s="147"/>
+      <c r="E24" s="147"/>
+      <c r="F24" s="104"/>
     </row>
     <row r="25" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="32"/>
       <c r="B25" s="29">
         <v>6</v>
       </c>
-      <c r="C25" s="153" t="s">
-        <v>117</v>
-      </c>
-      <c r="D25" s="154"/>
-      <c r="E25" s="154"/>
-      <c r="F25" s="155"/>
+      <c r="C25" s="170" t="s">
+        <v>114</v>
+      </c>
+      <c r="D25" s="171"/>
+      <c r="E25" s="171"/>
+      <c r="F25" s="172"/>
     </row>
     <row r="26" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="30" t="s">
@@ -4283,48 +4265,48 @@
       <c r="B26" s="31">
         <v>2</v>
       </c>
-      <c r="C26" s="255"/>
-      <c r="D26" s="256"/>
-      <c r="E26" s="256" t="s">
-        <v>71</v>
-      </c>
-      <c r="F26" s="257"/>
+      <c r="C26" s="273"/>
+      <c r="D26" s="274"/>
+      <c r="E26" s="274" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="275"/>
     </row>
     <row r="27" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="33"/>
       <c r="B27" s="27">
         <v>3</v>
       </c>
-      <c r="C27" s="83"/>
-      <c r="D27" s="84"/>
-      <c r="E27" s="84" t="s">
-        <v>71</v>
-      </c>
-      <c r="F27" s="85"/>
+      <c r="C27" s="115"/>
+      <c r="D27" s="116"/>
+      <c r="E27" s="116" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27" s="117"/>
     </row>
     <row r="28" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="33"/>
       <c r="B28" s="27">
         <v>4</v>
       </c>
-      <c r="C28" s="83" t="s">
-        <v>72</v>
-      </c>
-      <c r="D28" s="84"/>
-      <c r="E28" s="84"/>
-      <c r="F28" s="85"/>
+      <c r="C28" s="115" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" s="116"/>
+      <c r="E28" s="116"/>
+      <c r="F28" s="117"/>
     </row>
     <row r="29" spans="1:6" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="34"/>
       <c r="B29" s="29">
         <v>5</v>
       </c>
-      <c r="C29" s="262" t="s">
-        <v>72</v>
-      </c>
-      <c r="D29" s="263"/>
-      <c r="E29" s="264"/>
-      <c r="F29" s="265"/>
+      <c r="C29" s="266" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" s="267"/>
+      <c r="E29" s="268"/>
+      <c r="F29" s="269"/>
     </row>
     <row r="30" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="35" t="s">
@@ -4333,52 +4315,52 @@
       <c r="B30" s="25">
         <v>1</v>
       </c>
-      <c r="C30" s="147"/>
-      <c r="D30" s="266"/>
-      <c r="E30" s="267" t="s">
-        <v>122</v>
-      </c>
-      <c r="F30" s="268"/>
+      <c r="C30" s="138"/>
+      <c r="D30" s="270"/>
+      <c r="E30" s="271" t="s">
+        <v>119</v>
+      </c>
+      <c r="F30" s="258"/>
     </row>
     <row r="31" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="47"/>
       <c r="B31" s="25">
         <v>2</v>
       </c>
-      <c r="C31" s="83" t="s">
-        <v>120</v>
-      </c>
-      <c r="D31" s="84"/>
-      <c r="E31" s="84" t="s">
-        <v>122</v>
-      </c>
-      <c r="F31" s="85"/>
+      <c r="C31" s="115" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31" s="116"/>
+      <c r="E31" s="116" t="s">
+        <v>119</v>
+      </c>
+      <c r="F31" s="117"/>
     </row>
     <row r="32" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="36"/>
       <c r="B32" s="62">
         <v>3</v>
       </c>
-      <c r="C32" s="89" t="s">
-        <v>123</v>
-      </c>
-      <c r="D32" s="269"/>
-      <c r="E32" s="130" t="s">
-        <v>121</v>
-      </c>
-      <c r="F32" s="91"/>
+      <c r="C32" s="75" t="s">
+        <v>120</v>
+      </c>
+      <c r="D32" s="272"/>
+      <c r="E32" s="97" t="s">
+        <v>118</v>
+      </c>
+      <c r="F32" s="77"/>
     </row>
     <row r="33" spans="1:6" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="48"/>
       <c r="B33" s="49">
         <v>4</v>
       </c>
-      <c r="C33" s="258" t="s">
-        <v>123</v>
-      </c>
-      <c r="D33" s="259"/>
-      <c r="E33" s="260"/>
-      <c r="F33" s="261"/>
+      <c r="C33" s="262" t="s">
+        <v>120</v>
+      </c>
+      <c r="D33" s="263"/>
+      <c r="E33" s="264"/>
+      <c r="F33" s="265"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34" s="2" t="s">
@@ -4398,6 +4380,25 @@
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="C31:D31"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C15:F15"/>
@@ -4413,25 +4414,6 @@
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="C24:F24"/>
   </mergeCells>
   <conditionalFormatting sqref="C8">
     <cfRule type="expression" priority="1">

--- a/input/timetable/ИТиСС.xlsx
+++ b/input/timetable/ИТиСС.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="29010" windowHeight="14340" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="29010" windowHeight="14340"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="162">
   <si>
     <t>пара</t>
   </si>
@@ -71,6 +71,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -125,21 +128,45 @@
     <t>ТО</t>
   </si>
   <si>
+    <t>Пешков А.А.</t>
+  </si>
+  <si>
+    <t>Иванов Г.В.</t>
+  </si>
+  <si>
+    <t>Семенова Л.Л.</t>
+  </si>
+  <si>
     <t>Физическая культура и спорт (лек 8 ч)</t>
   </si>
   <si>
+    <t>Чаппаров Ф.Х.</t>
+  </si>
+  <si>
     <t>Электромагнитные поля и волны (лек), У902</t>
   </si>
   <si>
     <t>Электроника (лек), У902</t>
   </si>
   <si>
+    <t>Демко А.И.</t>
+  </si>
+  <si>
+    <t>Рыжаков В.В.</t>
+  </si>
+  <si>
     <t>День самостоятельной работы</t>
   </si>
   <si>
     <t>604-31</t>
   </si>
   <si>
+    <t>Иванов А.В.</t>
+  </si>
+  <si>
+    <t>Сальников В.Г.</t>
+  </si>
+  <si>
     <t>Электроника, п/г 1, У306//</t>
   </si>
   <si>
@@ -161,6 +188,12 @@
     <t>Элект. дисциплины по физич. культуре и спорту проводятся  1 парой или  2 парой в зависимости от выбранной элективной дисциплины., занятия в объеме 16 часов провдятся по отдельному расписанию.</t>
   </si>
   <si>
+    <t>Бычин И.В</t>
+  </si>
+  <si>
+    <t>Заводовский А.Г.</t>
+  </si>
+  <si>
     <t>Иностранный язык, п/г 1, У507</t>
   </si>
   <si>
@@ -194,9 +227,15 @@
     <t>Правоведение (лек 32 ч)</t>
   </si>
   <si>
+    <t>Никонова Н.П.</t>
+  </si>
+  <si>
     <t>Технологии сетей радиодоступа, п/г 1, У304//</t>
   </si>
   <si>
+    <t>Бабкин А.Ю.</t>
+  </si>
+  <si>
     <t>Электропитание устройств телекоммуникаций, п/г 1, А332//</t>
   </si>
   <si>
@@ -206,6 +245,9 @@
     <t>Начальник УОпоОФО</t>
   </si>
   <si>
+    <t>Мостовенко Л.В./Демко А.И.</t>
+  </si>
+  <si>
     <t>Технико-экономическое обоснование инженерных проектов (пр), ЭОиДОТ</t>
   </si>
   <si>
@@ -257,18 +299,30 @@
     <t>Корпоративные инфокоммуникационные системы и сети                                                             ТО: 02.02.2026-04.04.2026</t>
   </si>
   <si>
+    <t>Хадынская А.А.</t>
+  </si>
+  <si>
     <t>Основы российской государственности (лек 16 ч)</t>
   </si>
   <si>
+    <t>Власюк Е.И.</t>
+  </si>
+  <si>
     <t>Введение в инжиниринг (пр), ЭОиДОТ//</t>
   </si>
   <si>
+    <t>Калачиков А.М.</t>
+  </si>
+  <si>
     <t>Физика, п/г 1, А316//</t>
   </si>
   <si>
     <t>//Физика, п/г 2, А316</t>
   </si>
   <si>
+    <t>Чеснокова Н.Е.; Чаппаров Ф.Х.</t>
+  </si>
+  <si>
     <t>Электротехника и электроника, п/г 2, У301</t>
   </si>
   <si>
@@ -281,6 +335,9 @@
     <t>Электротехника и электроника (лек)/(пр), У902</t>
   </si>
   <si>
+    <t>Семенова Л.Л./Заводовский А.Г.</t>
+  </si>
+  <si>
     <t>Электротехника и электроника (пр), У506// Физика (пр), А305</t>
   </si>
   <si>
@@ -296,18 +353,39 @@
     <t>Работа в команде (лек 32 ч)</t>
   </si>
   <si>
+    <t>Биек А.В.</t>
+  </si>
+  <si>
     <t>Безопасность жизнедеятельности (лек 32 ч)</t>
   </si>
   <si>
+    <t>Мягких К.П.</t>
+  </si>
+  <si>
+    <t>Демко А.И.; Костюнина М.В.</t>
+  </si>
+  <si>
+    <t>Мостовенко Л.В.;Демко А.И.</t>
+  </si>
+  <si>
+    <t>Чеснокова Н.Е.;Мостовенко Л.В.</t>
+  </si>
+  <si>
     <t>Основы проектной деятельности (лек 16 ч)</t>
   </si>
   <si>
+    <t>Герасимова Н.Н.</t>
+  </si>
+  <si>
     <t>Ремонт и обслуживание простых контрольно-измерительных приборов, п/г 2, У306</t>
   </si>
   <si>
     <t>Ремонт и обслуживание простых контрольно-измерительных приборов, п/г 1, У306</t>
   </si>
   <si>
+    <t xml:space="preserve"> Костюнина М.В.</t>
+  </si>
+  <si>
     <t>Инженерная и компьютерная графика (лек), У903// Электроника  (пр), У304</t>
   </si>
   <si>
@@ -326,6 +404,21 @@
     <t xml:space="preserve"> Электромагнитные поля и волны (пр), У305</t>
   </si>
   <si>
+    <t>Ашарин А.А.</t>
+  </si>
+  <si>
+    <t>Курц М.А.</t>
+  </si>
+  <si>
+    <t>Арасланов Р.Ф.</t>
+  </si>
+  <si>
+    <t>Семенова Л.Л./Бабкин А.Ю.: Бабкин А.Ю./Семенова Л.Л.</t>
+  </si>
+  <si>
+    <t>Арасланов Р.Ф./Сальников В.Г.</t>
+  </si>
+  <si>
     <t>Технико-экономическое обоснование инженерных проектов (лек), ЭОиДОТ//  Электропитание устройств телекоммуникаций (лек 8ч), ЭОиДОТ</t>
   </si>
   <si>
@@ -371,6 +464,15 @@
     <t>Управление радиочастотным спектром и электромагнитная совместимость (лек), У304</t>
   </si>
   <si>
+    <t>Авдеев В.В.</t>
+  </si>
+  <si>
+    <t>Азиева М.Т.; Авдеев В.В.</t>
+  </si>
+  <si>
+    <t>Авдеев В.В.; Азиева М.Т.</t>
+  </si>
+  <si>
     <t>Управление радиочастотным спектром и электромагнитная совместимость (пр), У306</t>
   </si>
   <si>
@@ -399,6 +501,12 @@
   </si>
   <si>
     <t>Информационная безопасность систем связи и телекоммуникаций (пр), ЭОиДОТ</t>
+  </si>
+  <si>
+    <t>Чаппаров Ф.Х.; Свириденко М.А.</t>
+  </si>
+  <si>
+    <t>Свириденко М.А.</t>
   </si>
 </sst>
 </file>
@@ -516,7 +624,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -535,6 +643,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -546,7 +660,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="62">
+  <borders count="65">
     <border>
       <left/>
       <right/>
@@ -663,6 +777,34 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1278,6 +1420,19 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1323,7 +1478,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="276">
+  <cellXfs count="309">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1364,28 +1519,31 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1400,12 +1558,14 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1415,26 +1575,27 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1446,35 +1607,40 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1486,432 +1652,327 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1923,102 +1984,231 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2328,7 +2518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2337,78 +2527,79 @@
     <col min="4" max="4" width="16.85546875" style="2" customWidth="1"/>
     <col min="5" max="5" width="17.85546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.85546875" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A1" s="64" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="66" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="75" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" s="64" t="s">
-        <v>60</v>
-      </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="66" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A2" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="75" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" s="64" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="66" t="s">
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="75" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="67" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F4" s="76" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -2418,46 +2609,46 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="105" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="105"/>
-      <c r="E7" s="46" t="s">
-        <v>74</v>
+      <c r="D7" s="106"/>
+      <c r="E7" s="50" t="s">
+        <v>88</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="16"/>
     </row>
-    <row r="9" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="16"/>
     </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>0</v>
@@ -2468,335 +2659,414 @@
       <c r="D10" s="21"/>
       <c r="E10" s="22"/>
       <c r="F10" s="23"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="25">
+      <c r="G10" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="26">
         <v>2</v>
       </c>
-      <c r="C11" s="130"/>
-      <c r="D11" s="131"/>
-      <c r="E11" s="131"/>
-      <c r="F11" s="132"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="26"/>
-      <c r="B12" s="27">
+      <c r="C11" s="134"/>
+      <c r="D11" s="135"/>
+      <c r="E11" s="135"/>
+      <c r="F11" s="136"/>
+      <c r="G11" s="85"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="27"/>
+      <c r="B12" s="28">
         <v>3</v>
       </c>
-      <c r="C12" s="75" t="s">
-        <v>85</v>
-      </c>
-      <c r="D12" s="76"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="77"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="26"/>
-      <c r="B13" s="27">
+      <c r="C12" s="122" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="123"/>
+      <c r="E12" s="123"/>
+      <c r="F12" s="124"/>
+      <c r="G12" s="85" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="27"/>
+      <c r="B13" s="28">
         <v>4</v>
       </c>
-      <c r="C13" s="115" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" s="116"/>
-      <c r="E13" s="116"/>
-      <c r="F13" s="117"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="28"/>
-      <c r="B14" s="29">
+      <c r="C13" s="116" t="s">
+        <v>105</v>
+      </c>
+      <c r="D13" s="117"/>
+      <c r="E13" s="117"/>
+      <c r="F13" s="118"/>
+      <c r="G13" s="85" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="29"/>
+      <c r="B14" s="30">
         <v>6</v>
       </c>
-      <c r="C14" s="78" t="s">
-        <v>79</v>
-      </c>
-      <c r="D14" s="79"/>
-      <c r="E14" s="79"/>
-      <c r="F14" s="80"/>
-    </row>
-    <row r="15" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="31">
+      <c r="C14" s="144" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" s="145"/>
+      <c r="E14" s="145"/>
+      <c r="F14" s="146"/>
+      <c r="G14" s="92" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="33">
         <v>1</v>
       </c>
-      <c r="C15" s="118" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" s="119"/>
-      <c r="E15" s="119"/>
-      <c r="F15" s="120"/>
-    </row>
-    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27">
+      <c r="C15" s="119" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" s="120"/>
+      <c r="E15" s="120"/>
+      <c r="F15" s="121"/>
+      <c r="G15" s="86" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="27"/>
+      <c r="B16" s="28">
         <v>2</v>
       </c>
-      <c r="C16" s="112" t="s">
-        <v>122</v>
-      </c>
-      <c r="D16" s="113"/>
-      <c r="E16" s="113"/>
-      <c r="F16" s="114"/>
-    </row>
-    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="26"/>
-      <c r="B17" s="27">
+      <c r="C16" s="113" t="s">
+        <v>156</v>
+      </c>
+      <c r="D16" s="114"/>
+      <c r="E16" s="114"/>
+      <c r="F16" s="115"/>
+      <c r="G16" s="85" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="27"/>
+      <c r="B17" s="28">
         <v>3</v>
       </c>
-      <c r="C17" s="133"/>
-      <c r="D17" s="134"/>
-      <c r="E17" s="134"/>
-      <c r="F17" s="135"/>
-    </row>
-    <row r="18" spans="1:6" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="32"/>
-      <c r="B18" s="29">
+      <c r="C17" s="137"/>
+      <c r="D17" s="138"/>
+      <c r="E17" s="138"/>
+      <c r="F17" s="139"/>
+      <c r="G17" s="79"/>
+    </row>
+    <row r="18" spans="1:7" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="35"/>
+      <c r="B18" s="30">
         <v>5</v>
       </c>
-      <c r="C18" s="121" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="123"/>
-    </row>
-    <row r="19" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="31">
+      <c r="C18" s="125" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="126"/>
+      <c r="E18" s="126"/>
+      <c r="F18" s="127"/>
+      <c r="G18" s="84" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="33">
         <v>1</v>
       </c>
-      <c r="C19" s="127" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="128"/>
-      <c r="E19" s="128" t="s">
+      <c r="C19" s="131" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="132"/>
+      <c r="E19" s="132" t="s">
+        <v>118</v>
+      </c>
+      <c r="F19" s="133"/>
+      <c r="G19" s="93" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="27"/>
+      <c r="B20" s="28">
+        <v>2</v>
+      </c>
+      <c r="C20" s="116" t="s">
+        <v>119</v>
+      </c>
+      <c r="D20" s="117"/>
+      <c r="E20" s="117" t="s">
+        <v>100</v>
+      </c>
+      <c r="F20" s="118"/>
+      <c r="G20" s="85" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="27"/>
+      <c r="B21" s="28">
+        <v>3</v>
+      </c>
+      <c r="C21" s="140" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" s="141"/>
+      <c r="E21" s="142"/>
+      <c r="F21" s="143"/>
+      <c r="G21" s="85" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="33">
+        <v>1</v>
+      </c>
+      <c r="C22" s="128" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" s="129"/>
+      <c r="E22" s="129"/>
+      <c r="F22" s="130"/>
+      <c r="G22" s="86" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="27"/>
+      <c r="B23" s="28">
+        <v>2</v>
+      </c>
+      <c r="C23" s="122" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" s="123"/>
+      <c r="E23" s="123"/>
+      <c r="F23" s="124"/>
+      <c r="G23" s="85" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="27"/>
+      <c r="B24" s="28">
+        <v>3</v>
+      </c>
+      <c r="C24" s="150"/>
+      <c r="D24" s="151"/>
+      <c r="E24" s="151"/>
+      <c r="F24" s="152"/>
+      <c r="G24" s="79"/>
+    </row>
+    <row r="25" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="35"/>
+      <c r="B25" s="30">
+        <v>4</v>
+      </c>
+      <c r="C25" s="153"/>
+      <c r="D25" s="154"/>
+      <c r="E25" s="154"/>
+      <c r="F25" s="143"/>
+      <c r="G25" s="83"/>
+    </row>
+    <row r="26" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="33">
+        <v>1</v>
+      </c>
+      <c r="C26" s="161"/>
+      <c r="D26" s="162"/>
+      <c r="E26" s="163" t="s">
+        <v>102</v>
+      </c>
+      <c r="F26" s="124"/>
+      <c r="G26" s="85" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="36"/>
+      <c r="B27" s="28">
+        <v>2</v>
+      </c>
+      <c r="C27" s="122" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="123"/>
+      <c r="E27" s="123"/>
+      <c r="F27" s="124"/>
+      <c r="G27" s="85" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="36"/>
+      <c r="B28" s="28">
+        <v>3</v>
+      </c>
+      <c r="C28" s="158" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="159"/>
+      <c r="E28" s="159"/>
+      <c r="F28" s="160"/>
+      <c r="G28" s="85" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="37"/>
+      <c r="B29" s="30">
+        <v>4</v>
+      </c>
+      <c r="C29" s="107"/>
+      <c r="D29" s="108"/>
+      <c r="E29" s="108"/>
+      <c r="F29" s="109"/>
+      <c r="G29" s="78"/>
+    </row>
+    <row r="30" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="26">
+        <v>2</v>
+      </c>
+      <c r="C30" s="155"/>
+      <c r="D30" s="156"/>
+      <c r="E30" s="156"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="81"/>
+    </row>
+    <row r="31" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="39"/>
+      <c r="B31" s="26">
+        <v>3</v>
+      </c>
+      <c r="C31" s="167" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" s="168"/>
+      <c r="E31" s="169" t="s">
+        <v>98</v>
+      </c>
+      <c r="F31" s="170"/>
+      <c r="G31" s="93" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="39"/>
+      <c r="B32" s="26">
+        <v>4</v>
+      </c>
+      <c r="C32" s="150"/>
+      <c r="D32" s="151"/>
+      <c r="E32" s="151"/>
+      <c r="F32" s="152"/>
+      <c r="G32" s="81"/>
+    </row>
+    <row r="33" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="39"/>
+      <c r="B33" s="40">
+        <v>5</v>
+      </c>
+      <c r="C33" s="153"/>
+      <c r="D33" s="154"/>
+      <c r="E33" s="154"/>
+      <c r="F33" s="143"/>
+      <c r="G33" s="31"/>
+    </row>
+    <row r="34" spans="1:7" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="41"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="110"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="111"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="43"/>
+    </row>
+    <row r="35" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="88"/>
+      <c r="B35" s="89" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="164" t="s">
         <v>93</v>
       </c>
-      <c r="F19" s="129"/>
-    </row>
-    <row r="20" spans="1:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27">
-        <v>2</v>
-      </c>
-      <c r="C20" s="115" t="s">
+      <c r="D35" s="165"/>
+      <c r="E35" s="165"/>
+      <c r="F35" s="166"/>
+      <c r="G35" s="91" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="116"/>
-      <c r="E20" s="116" t="s">
-        <v>82</v>
-      </c>
-      <c r="F20" s="117"/>
-    </row>
-    <row r="21" spans="1:6" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="26"/>
-      <c r="B21" s="27">
-        <v>3</v>
-      </c>
-      <c r="C21" s="136" t="s">
-        <v>83</v>
-      </c>
-      <c r="D21" s="137"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="74"/>
-    </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="31">
-        <v>1</v>
-      </c>
-      <c r="C22" s="124" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" s="125"/>
-      <c r="E22" s="125"/>
-      <c r="F22" s="126"/>
-    </row>
-    <row r="23" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="26"/>
-      <c r="B23" s="27">
-        <v>2</v>
-      </c>
-      <c r="C23" s="75" t="s">
-        <v>89</v>
-      </c>
-      <c r="D23" s="76"/>
-      <c r="E23" s="76"/>
-      <c r="F23" s="77"/>
-    </row>
-    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="26"/>
-      <c r="B24" s="27">
-        <v>3</v>
-      </c>
-      <c r="C24" s="84"/>
-      <c r="D24" s="85"/>
-      <c r="E24" s="85"/>
-      <c r="F24" s="86"/>
-    </row>
-    <row r="25" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="32"/>
-      <c r="B25" s="29">
-        <v>4</v>
-      </c>
-      <c r="C25" s="87"/>
-      <c r="D25" s="88"/>
-      <c r="E25" s="88"/>
-      <c r="F25" s="74"/>
-    </row>
-    <row r="26" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="31">
-        <v>1</v>
-      </c>
-      <c r="C26" s="95"/>
-      <c r="D26" s="96"/>
-      <c r="E26" s="97" t="s">
-        <v>84</v>
-      </c>
-      <c r="F26" s="77"/>
-    </row>
-    <row r="27" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="33"/>
-      <c r="B27" s="27">
-        <v>2</v>
-      </c>
-      <c r="C27" s="75" t="s">
-        <v>47</v>
-      </c>
-      <c r="D27" s="76"/>
-      <c r="E27" s="76"/>
-      <c r="F27" s="77"/>
-    </row>
-    <row r="28" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="33"/>
-      <c r="B28" s="27">
-        <v>3</v>
-      </c>
-      <c r="C28" s="92" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" s="93"/>
-      <c r="E28" s="93"/>
-      <c r="F28" s="94"/>
-    </row>
-    <row r="29" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="34"/>
-      <c r="B29" s="29">
-        <v>4</v>
-      </c>
-      <c r="C29" s="106"/>
-      <c r="D29" s="107"/>
-      <c r="E29" s="107"/>
-      <c r="F29" s="108"/>
-    </row>
-    <row r="30" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="25">
-        <v>2</v>
-      </c>
-      <c r="C30" s="89"/>
-      <c r="D30" s="90"/>
-      <c r="E30" s="90"/>
-      <c r="F30" s="91"/>
-    </row>
-    <row r="31" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="36"/>
-      <c r="B31" s="25">
-        <v>3</v>
-      </c>
-      <c r="C31" s="101" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31" s="102"/>
-      <c r="E31" s="103" t="s">
-        <v>81</v>
-      </c>
-      <c r="F31" s="104"/>
-    </row>
-    <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="36"/>
-      <c r="B32" s="25">
-        <v>4</v>
-      </c>
-      <c r="C32" s="84"/>
-      <c r="D32" s="85"/>
-      <c r="E32" s="85"/>
-      <c r="F32" s="86"/>
-    </row>
-    <row r="33" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="36"/>
-      <c r="B33" s="37">
-        <v>5</v>
-      </c>
-      <c r="C33" s="87"/>
-      <c r="D33" s="88"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="74"/>
-    </row>
-    <row r="34" spans="1:6" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="38"/>
-      <c r="B34" s="39"/>
-      <c r="C34" s="109"/>
-      <c r="D34" s="110"/>
-      <c r="E34" s="110"/>
-      <c r="F34" s="111"/>
-    </row>
-    <row r="35" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="68"/>
-      <c r="B35" s="69" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="98" t="s">
-        <v>78</v>
-      </c>
-      <c r="D35" s="99"/>
-      <c r="E35" s="99"/>
-      <c r="F35" s="100"/>
-    </row>
-    <row r="36" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="45"/>
-      <c r="B36" s="70" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="81" t="s">
-        <v>34</v>
-      </c>
-      <c r="D36" s="82"/>
-      <c r="E36" s="82"/>
-      <c r="F36" s="83"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="36" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="49"/>
+      <c r="B36" s="90" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="147" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" s="148"/>
+      <c r="E36" s="148"/>
+      <c r="F36" s="149"/>
+      <c r="G36" s="87" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C25:F25"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="C34:F34"/>
@@ -2813,22 +3083,6 @@
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:E9">
     <cfRule type="expression" priority="2">
@@ -2856,7 +3110,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2865,46 +3119,47 @@
     <col min="4" max="4" width="18.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A1" s="64" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="66" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="75" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" s="64" t="s">
-        <v>60</v>
-      </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="66" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A2" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="75" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" s="64" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="66" t="s">
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="75" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
@@ -2912,31 +3167,31 @@
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="67" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F4" s="76" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -2946,432 +3201,479 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="105" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="105"/>
-      <c r="E7" s="46" t="s">
-        <v>40</v>
+      <c r="D7" s="106"/>
+      <c r="E7" s="50" t="s">
+        <v>49</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="16"/>
     </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="143" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="143"/>
+        <v>34</v>
+      </c>
+      <c r="C9" s="204" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="204"/>
       <c r="E9" s="17"/>
       <c r="F9" s="16"/>
     </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="42"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="44"/>
-    </row>
-    <row r="11" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="31">
+      <c r="D10" s="46"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="33">
         <v>1</v>
       </c>
-      <c r="C11" s="144" t="s">
-        <v>95</v>
-      </c>
-      <c r="D11" s="145"/>
-      <c r="E11" s="145"/>
-      <c r="F11" s="146"/>
-    </row>
-    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="26"/>
-      <c r="B12" s="27">
+      <c r="C11" s="205" t="s">
+        <v>121</v>
+      </c>
+      <c r="D11" s="206"/>
+      <c r="E11" s="206"/>
+      <c r="F11" s="207"/>
+      <c r="G11" s="99" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="27"/>
+      <c r="B12" s="28">
         <v>2</v>
       </c>
-      <c r="C12" s="101" t="s">
+      <c r="C12" s="167" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="208"/>
+      <c r="E12" s="208"/>
+      <c r="F12" s="170"/>
+      <c r="G12" s="85" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="27"/>
+      <c r="B13" s="28">
+        <v>3</v>
+      </c>
+      <c r="C13" s="167" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="208"/>
+      <c r="E13" s="208"/>
+      <c r="F13" s="170"/>
+      <c r="G13" s="94" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="27"/>
+      <c r="B14" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="209" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="147"/>
-      <c r="E12" s="147"/>
-      <c r="F12" s="104"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="26"/>
-      <c r="B13" s="27">
+      <c r="D14" s="210"/>
+      <c r="E14" s="210"/>
+      <c r="F14" s="211"/>
+      <c r="G14" s="71"/>
+    </row>
+    <row r="15" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="33">
+        <v>2</v>
+      </c>
+      <c r="C15" s="131" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="132"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="99" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="27"/>
+      <c r="B16" s="28">
         <v>3</v>
       </c>
-      <c r="C13" s="101" t="s">
+      <c r="C16" s="217" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="218"/>
+      <c r="E16" s="218"/>
+      <c r="F16" s="219"/>
+      <c r="G16" s="94" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="27"/>
+      <c r="B17" s="28">
+        <v>4</v>
+      </c>
+      <c r="C17" s="113" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="114"/>
+      <c r="E17" s="114" t="s">
+        <v>122</v>
+      </c>
+      <c r="F17" s="115"/>
+      <c r="G17" s="94" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="35"/>
+      <c r="B18" s="30">
+        <v>5</v>
+      </c>
+      <c r="C18" s="125" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="215"/>
+      <c r="E18" s="216" t="s">
+        <v>81</v>
+      </c>
+      <c r="F18" s="127"/>
+      <c r="G18" s="87" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="33">
+        <v>1</v>
+      </c>
+      <c r="C19" s="212"/>
+      <c r="D19" s="213"/>
+      <c r="E19" s="213"/>
+      <c r="F19" s="214"/>
+      <c r="G19" s="79"/>
+    </row>
+    <row r="20" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="27"/>
+      <c r="B20" s="28">
+        <v>2</v>
+      </c>
+      <c r="C20" s="220" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="177"/>
+      <c r="E20" s="177" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" s="178"/>
+      <c r="G20" s="85" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="27"/>
+      <c r="B21" s="28">
+        <v>3</v>
+      </c>
+      <c r="C21" s="116" t="s">
+        <v>123</v>
+      </c>
+      <c r="D21" s="117"/>
+      <c r="E21" s="117" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" s="118"/>
+      <c r="G21" s="85" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="35"/>
+      <c r="B22" s="30">
+        <v>4</v>
+      </c>
+      <c r="C22" s="183" t="s">
+        <v>124</v>
+      </c>
+      <c r="D22" s="184"/>
+      <c r="E22" s="184"/>
+      <c r="F22" s="185"/>
+      <c r="G22" s="84" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="33">
+        <v>1</v>
+      </c>
+      <c r="C23" s="180"/>
+      <c r="D23" s="181"/>
+      <c r="E23" s="181"/>
+      <c r="F23" s="182"/>
+      <c r="G23" s="34"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="27"/>
+      <c r="B24" s="28">
+        <v>2</v>
+      </c>
+      <c r="C24" s="122" t="s">
+        <v>125</v>
+      </c>
+      <c r="D24" s="123"/>
+      <c r="E24" s="123"/>
+      <c r="F24" s="124"/>
+      <c r="G24" s="92" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="27"/>
+      <c r="B25" s="28">
+        <v>3</v>
+      </c>
+      <c r="C25" s="122" t="s">
+        <v>140</v>
+      </c>
+      <c r="D25" s="123"/>
+      <c r="E25" s="123"/>
+      <c r="F25" s="124"/>
+      <c r="G25" s="85" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="35"/>
+      <c r="B26" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="186" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="187"/>
+      <c r="E26" s="187"/>
+      <c r="F26" s="188"/>
+      <c r="G26" s="78"/>
+    </row>
+    <row r="27" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="33">
+        <v>2</v>
+      </c>
+      <c r="C27" s="180"/>
+      <c r="D27" s="181"/>
+      <c r="E27" s="181"/>
+      <c r="F27" s="182"/>
+      <c r="G27" s="34"/>
+    </row>
+    <row r="28" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="36"/>
+      <c r="B28" s="28">
+        <v>3</v>
+      </c>
+      <c r="C28" s="150"/>
+      <c r="D28" s="151"/>
+      <c r="E28" s="151"/>
+      <c r="F28" s="152"/>
+      <c r="G28" s="79"/>
+    </row>
+    <row r="29" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="36"/>
+      <c r="B29" s="28">
+        <v>4</v>
+      </c>
+      <c r="C29" s="198" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="199"/>
+      <c r="E29" s="199"/>
+      <c r="F29" s="200"/>
+      <c r="G29" s="97" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="37"/>
+      <c r="B30" s="30">
+        <v>5</v>
+      </c>
+      <c r="C30" s="201" t="s">
+        <v>126</v>
+      </c>
+      <c r="D30" s="202"/>
+      <c r="E30" s="202"/>
+      <c r="F30" s="203"/>
+      <c r="G30" s="84" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="55" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="33">
+        <v>2</v>
+      </c>
+      <c r="C31" s="174" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" s="175"/>
+      <c r="E31" s="175"/>
+      <c r="F31" s="176"/>
+      <c r="G31" s="34"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B32" s="70">
+        <v>3</v>
+      </c>
+      <c r="C32" s="171"/>
+      <c r="D32" s="172"/>
+      <c r="E32" s="172"/>
+      <c r="F32" s="173"/>
+      <c r="G32" s="97"/>
+    </row>
+    <row r="33" spans="1:7" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="49"/>
+      <c r="B33" s="30">
+        <v>4</v>
+      </c>
+      <c r="C33" s="153"/>
+      <c r="D33" s="154"/>
+      <c r="E33" s="154"/>
+      <c r="F33" s="143"/>
+      <c r="G33" s="78"/>
+    </row>
+    <row r="34" spans="1:7" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="60"/>
+      <c r="B34" s="61"/>
+      <c r="C34" s="194"/>
+      <c r="D34" s="194"/>
+      <c r="E34" s="194"/>
+      <c r="F34" s="194"/>
+      <c r="G34" s="77"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="58"/>
+      <c r="B35" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="191" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" s="192"/>
+      <c r="E35" s="192"/>
+      <c r="F35" s="193"/>
+      <c r="G35" s="86" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="95"/>
+      <c r="B36" s="96" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="195" t="s">
+        <v>116</v>
+      </c>
+      <c r="D36" s="196"/>
+      <c r="E36" s="196"/>
+      <c r="F36" s="197"/>
+      <c r="G36" s="97" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="59"/>
+      <c r="B37" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="189" t="s">
+        <v>111</v>
+      </c>
+      <c r="D37" s="148"/>
+      <c r="E37" s="148"/>
+      <c r="F37" s="190"/>
+      <c r="G37" s="84" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="147"/>
-      <c r="E13" s="147"/>
-      <c r="F13" s="104"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="148" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="149"/>
-      <c r="E14" s="149"/>
-      <c r="F14" s="150"/>
-    </row>
-    <row r="15" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="31">
-        <v>2</v>
-      </c>
-      <c r="C15" s="127" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="128"/>
-      <c r="E15" s="128"/>
-      <c r="F15" s="129"/>
-    </row>
-    <row r="16" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27">
-        <v>3</v>
-      </c>
-      <c r="C16" s="156" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16" s="157"/>
-      <c r="E16" s="157"/>
-      <c r="F16" s="158"/>
-    </row>
-    <row r="17" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="26"/>
-      <c r="B17" s="27">
-        <v>4</v>
-      </c>
-      <c r="C17" s="112" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="113"/>
-      <c r="E17" s="113" t="s">
-        <v>96</v>
-      </c>
-      <c r="F17" s="114"/>
-    </row>
-    <row r="18" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="32"/>
-      <c r="B18" s="29">
-        <v>5</v>
-      </c>
-      <c r="C18" s="121" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="154"/>
-      <c r="E18" s="155" t="s">
-        <v>67</v>
-      </c>
-      <c r="F18" s="123"/>
-    </row>
-    <row r="19" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="31">
-        <v>1</v>
-      </c>
-      <c r="C19" s="151"/>
-      <c r="D19" s="152"/>
-      <c r="E19" s="152"/>
-      <c r="F19" s="153"/>
-    </row>
-    <row r="20" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27">
-        <v>2</v>
-      </c>
-      <c r="C20" s="141" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="142"/>
-      <c r="E20" s="142" t="s">
-        <v>51</v>
-      </c>
-      <c r="F20" s="165"/>
-    </row>
-    <row r="21" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="26"/>
-      <c r="B21" s="27">
-        <v>3</v>
-      </c>
-      <c r="C21" s="115" t="s">
-        <v>97</v>
-      </c>
-      <c r="D21" s="116"/>
-      <c r="E21" s="116" t="s">
-        <v>66</v>
-      </c>
-      <c r="F21" s="117"/>
-    </row>
-    <row r="22" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="32"/>
-      <c r="B22" s="29">
-        <v>4</v>
-      </c>
-      <c r="C22" s="167" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" s="168"/>
-      <c r="E22" s="168"/>
-      <c r="F22" s="169"/>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="31">
-        <v>1</v>
-      </c>
-      <c r="C23" s="138"/>
-      <c r="D23" s="139"/>
-      <c r="E23" s="139"/>
-      <c r="F23" s="140"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A24" s="26"/>
-      <c r="B24" s="27">
-        <v>2</v>
-      </c>
-      <c r="C24" s="75" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" s="76"/>
-      <c r="E24" s="76"/>
-      <c r="F24" s="77"/>
-    </row>
-    <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="26"/>
-      <c r="B25" s="27">
-        <v>3</v>
-      </c>
-      <c r="C25" s="75" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" s="76"/>
-      <c r="E25" s="76"/>
-      <c r="F25" s="77"/>
-    </row>
-    <row r="26" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="32"/>
-      <c r="B26" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" s="170" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="171"/>
-      <c r="E26" s="171"/>
-      <c r="F26" s="172"/>
-    </row>
-    <row r="27" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="31">
-        <v>2</v>
-      </c>
-      <c r="C27" s="138"/>
-      <c r="D27" s="139"/>
-      <c r="E27" s="139"/>
-      <c r="F27" s="140"/>
-    </row>
-    <row r="28" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="33"/>
-      <c r="B28" s="27">
-        <v>3</v>
-      </c>
-      <c r="C28" s="84"/>
-      <c r="D28" s="85"/>
-      <c r="E28" s="85"/>
-      <c r="F28" s="86"/>
-    </row>
-    <row r="29" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="33"/>
-      <c r="B29" s="27">
-        <v>4</v>
-      </c>
-      <c r="C29" s="182" t="s">
-        <v>35</v>
-      </c>
-      <c r="D29" s="183"/>
-      <c r="E29" s="183"/>
-      <c r="F29" s="184"/>
-    </row>
-    <row r="30" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="34"/>
-      <c r="B30" s="29">
-        <v>5</v>
-      </c>
-      <c r="C30" s="185" t="s">
-        <v>100</v>
-      </c>
-      <c r="D30" s="186"/>
-      <c r="E30" s="186"/>
-      <c r="F30" s="187"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="31">
-        <v>2</v>
-      </c>
-      <c r="C31" s="162" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31" s="163"/>
-      <c r="E31" s="163"/>
-      <c r="F31" s="164"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B32" s="62">
-        <v>3</v>
-      </c>
-      <c r="C32" s="159"/>
-      <c r="D32" s="160"/>
-      <c r="E32" s="160"/>
-      <c r="F32" s="161"/>
-    </row>
-    <row r="33" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="45"/>
-      <c r="B33" s="29">
-        <v>4</v>
-      </c>
-      <c r="C33" s="87"/>
-      <c r="D33" s="88"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="74"/>
-    </row>
-    <row r="34" spans="1:6" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="55"/>
-      <c r="B34" s="56"/>
-      <c r="C34" s="178"/>
-      <c r="D34" s="178"/>
-      <c r="E34" s="178"/>
-      <c r="F34" s="178"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="53"/>
-      <c r="B35" s="51" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="175" t="s">
-        <v>90</v>
-      </c>
-      <c r="D35" s="176"/>
-      <c r="E35" s="176"/>
-      <c r="F35" s="177"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="71"/>
-      <c r="B36" s="72" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="179" t="s">
-        <v>92</v>
-      </c>
-      <c r="D36" s="180"/>
-      <c r="E36" s="180"/>
-      <c r="F36" s="181"/>
-    </row>
-    <row r="37" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="54"/>
-      <c r="B37" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="C37" s="173" t="s">
-        <v>91</v>
-      </c>
-      <c r="D37" s="82"/>
-      <c r="E37" s="82"/>
-      <c r="F37" s="174"/>
-    </row>
-    <row r="38" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="60" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="61"/>
-      <c r="C38" s="166" t="s">
-        <v>49</v>
-      </c>
-      <c r="D38" s="166"/>
-      <c r="E38" s="166"/>
-      <c r="F38" s="166"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B38" s="68"/>
+      <c r="C38" s="179" t="s">
+        <v>60</v>
+      </c>
+      <c r="D38" s="179"/>
+      <c r="E38" s="179"/>
+      <c r="F38" s="179"/>
+      <c r="G38" s="66"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C20:D20"/>
@@ -3388,6 +3690,24 @@
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="E18:F18"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:E9">
     <cfRule type="expression" priority="3">
@@ -3420,7 +3740,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3429,10 +3749,11 @@
     <col min="4" max="4" width="20" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="19.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -3440,15 +3761,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -3456,7 +3777,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
@@ -3465,30 +3786,30 @@
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -3498,35 +3819,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="105" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="105"/>
-      <c r="E7" s="46" t="s">
-        <v>38</v>
+      <c r="D7" s="106"/>
+      <c r="E7" s="50" t="s">
+        <v>45</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="203" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" s="203"/>
-      <c r="E8" s="203"/>
-      <c r="F8" s="203"/>
-    </row>
-    <row r="9" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+      <c r="C8" s="272" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" s="272"/>
+      <c r="E8" s="272"/>
+      <c r="F8" s="272"/>
+    </row>
+    <row r="9" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>0</v>
@@ -3537,368 +3858,415 @@
       <c r="D9" s="21"/>
       <c r="E9" s="22"/>
       <c r="F9" s="23"/>
-    </row>
-    <row r="10" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="25"/>
-      <c r="C10" s="194"/>
-      <c r="D10" s="195"/>
-      <c r="E10" s="195"/>
-      <c r="F10" s="196"/>
-      <c r="K10" s="63"/>
-    </row>
-    <row r="11" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="26"/>
-      <c r="B11" s="25">
+      <c r="G9" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="26"/>
+      <c r="C10" s="263"/>
+      <c r="D10" s="264"/>
+      <c r="E10" s="264"/>
+      <c r="F10" s="265"/>
+      <c r="G10" s="104"/>
+      <c r="L10" s="72"/>
+    </row>
+    <row r="11" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="27"/>
+      <c r="B11" s="26">
         <v>4</v>
       </c>
-      <c r="C11" s="204" t="s">
-        <v>123</v>
-      </c>
-      <c r="D11" s="205"/>
-      <c r="E11" s="205"/>
-      <c r="F11" s="206"/>
-      <c r="K11" s="63"/>
-    </row>
-    <row r="12" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="26"/>
-      <c r="B12" s="27">
+      <c r="C11" s="241" t="s">
+        <v>157</v>
+      </c>
+      <c r="D11" s="242"/>
+      <c r="E11" s="242"/>
+      <c r="F11" s="243"/>
+      <c r="G11" s="101" t="s">
+        <v>43</v>
+      </c>
+      <c r="L11" s="72"/>
+    </row>
+    <row r="12" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="27"/>
+      <c r="B12" s="28">
         <v>5</v>
       </c>
-      <c r="C12" s="210" t="s">
-        <v>101</v>
-      </c>
-      <c r="D12" s="211"/>
-      <c r="E12" s="211"/>
-      <c r="F12" s="212"/>
-    </row>
-    <row r="13" spans="1:11" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="28"/>
-      <c r="B13" s="29">
+      <c r="C12" s="273" t="s">
+        <v>132</v>
+      </c>
+      <c r="D12" s="274"/>
+      <c r="E12" s="274"/>
+      <c r="F12" s="275"/>
+      <c r="G12" s="103" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="29"/>
+      <c r="B13" s="30">
         <v>6</v>
       </c>
-      <c r="C13" s="213" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" s="214"/>
-      <c r="E13" s="214"/>
-      <c r="F13" s="215"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A14" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="31">
+      <c r="C13" s="276" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="277"/>
+      <c r="E13" s="277"/>
+      <c r="F13" s="278"/>
+      <c r="G13" s="102" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A14" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="33">
         <v>1</v>
       </c>
-      <c r="C14" s="197" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" s="198"/>
-      <c r="E14" s="198"/>
-      <c r="F14" s="199"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A15" s="26"/>
-      <c r="B15" s="25">
+      <c r="C14" s="266" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="267"/>
+      <c r="E14" s="267"/>
+      <c r="F14" s="268"/>
+      <c r="G14" s="104" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A15" s="27"/>
+      <c r="B15" s="26">
         <v>2</v>
       </c>
-      <c r="C15" s="188" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" s="189"/>
-      <c r="E15" s="189"/>
-      <c r="F15" s="190"/>
-    </row>
-    <row r="16" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27">
+      <c r="C15" s="257" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="258"/>
+      <c r="E15" s="258"/>
+      <c r="F15" s="259"/>
+      <c r="G15" s="103" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="27"/>
+      <c r="B16" s="28">
         <v>3</v>
       </c>
-      <c r="C16" s="238" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" s="239"/>
-      <c r="E16" s="240" t="s">
-        <v>63</v>
-      </c>
-      <c r="F16" s="241"/>
-    </row>
-    <row r="17" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="32"/>
-      <c r="B17" s="29">
+      <c r="C16" s="224" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="225"/>
+      <c r="E16" s="226" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" s="227"/>
+      <c r="G16" s="101" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="35"/>
+      <c r="B17" s="30">
         <v>4</v>
       </c>
-      <c r="C17" s="200" t="s">
-        <v>102</v>
-      </c>
-      <c r="D17" s="201"/>
-      <c r="E17" s="201"/>
-      <c r="F17" s="202"/>
-    </row>
-    <row r="18" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="31">
+      <c r="C17" s="269" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="270"/>
+      <c r="E17" s="270"/>
+      <c r="F17" s="271"/>
+      <c r="G17" s="102" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="33">
         <v>3</v>
       </c>
-      <c r="C18" s="216" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="217"/>
-      <c r="E18" s="217" t="s">
-        <v>108</v>
-      </c>
-      <c r="F18" s="218"/>
-    </row>
-    <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27">
+      <c r="C18" s="279" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="280"/>
+      <c r="E18" s="280" t="s">
+        <v>139</v>
+      </c>
+      <c r="F18" s="281"/>
+      <c r="G18" s="104" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="27"/>
+      <c r="B19" s="28">
         <v>4</v>
       </c>
-      <c r="C19" s="204" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" s="205"/>
-      <c r="E19" s="205"/>
-      <c r="F19" s="206"/>
-    </row>
-    <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27">
+      <c r="C19" s="241" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="242"/>
+      <c r="E19" s="242"/>
+      <c r="F19" s="243"/>
+      <c r="G19" s="101" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="27"/>
+      <c r="B20" s="28">
         <v>5</v>
       </c>
-      <c r="C20" s="204"/>
-      <c r="D20" s="205"/>
-      <c r="E20" s="205"/>
-      <c r="F20" s="206"/>
-    </row>
-    <row r="21" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="32"/>
-      <c r="B21" s="29">
+      <c r="C20" s="241"/>
+      <c r="D20" s="242"/>
+      <c r="E20" s="242"/>
+      <c r="F20" s="243"/>
+      <c r="G20" s="101"/>
+    </row>
+    <row r="21" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="35"/>
+      <c r="B21" s="30">
         <v>6</v>
       </c>
-      <c r="C21" s="207"/>
-      <c r="D21" s="208"/>
-      <c r="E21" s="208"/>
-      <c r="F21" s="209"/>
-    </row>
-    <row r="22" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="31">
+      <c r="C21" s="228"/>
+      <c r="D21" s="229"/>
+      <c r="E21" s="229"/>
+      <c r="F21" s="230"/>
+      <c r="G21" s="102"/>
+    </row>
+    <row r="22" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="33">
         <v>3</v>
       </c>
-      <c r="C22" s="242"/>
-      <c r="D22" s="243"/>
-      <c r="E22" s="243"/>
-      <c r="F22" s="244"/>
-    </row>
-    <row r="23" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="26"/>
-      <c r="B23" s="27">
+      <c r="C22" s="231"/>
+      <c r="D22" s="232"/>
+      <c r="E22" s="232"/>
+      <c r="F22" s="233"/>
+      <c r="G22" s="54"/>
+    </row>
+    <row r="23" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="27"/>
+      <c r="B23" s="28">
         <v>4</v>
       </c>
-      <c r="C23" s="245" t="s">
-        <v>105</v>
-      </c>
-      <c r="D23" s="246"/>
-      <c r="E23" s="247"/>
-      <c r="F23" s="248"/>
-    </row>
-    <row r="24" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="26"/>
-      <c r="B24" s="27">
+      <c r="C23" s="234" t="s">
+        <v>136</v>
+      </c>
+      <c r="D23" s="235"/>
+      <c r="E23" s="236"/>
+      <c r="F23" s="237"/>
+      <c r="G23" s="101" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="27"/>
+      <c r="B24" s="28">
         <v>5</v>
       </c>
-      <c r="C24" s="245"/>
-      <c r="D24" s="246"/>
-      <c r="E24" s="247" t="s">
-        <v>121</v>
-      </c>
-      <c r="F24" s="248"/>
-    </row>
-    <row r="25" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="32"/>
-      <c r="B25" s="29">
+      <c r="C24" s="234"/>
+      <c r="D24" s="235"/>
+      <c r="E24" s="236" t="s">
+        <v>155</v>
+      </c>
+      <c r="F24" s="237"/>
+      <c r="G24" s="101" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="35"/>
+      <c r="B25" s="30">
         <v>6</v>
       </c>
-      <c r="C25" s="207" t="s">
-        <v>124</v>
-      </c>
-      <c r="D25" s="208"/>
-      <c r="E25" s="208"/>
-      <c r="F25" s="209"/>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" s="191" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="192"/>
-      <c r="E26" s="192"/>
-      <c r="F26" s="193"/>
-    </row>
-    <row r="27" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="33"/>
-      <c r="B27" s="27">
+      <c r="C25" s="228" t="s">
+        <v>158</v>
+      </c>
+      <c r="D25" s="229"/>
+      <c r="E25" s="229"/>
+      <c r="F25" s="230"/>
+      <c r="G25" s="102" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="260" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="261"/>
+      <c r="E26" s="261"/>
+      <c r="F26" s="262"/>
+      <c r="G26" s="54"/>
+    </row>
+    <row r="27" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="36"/>
+      <c r="B27" s="28">
         <v>4</v>
       </c>
-      <c r="C27" s="235" t="s">
-        <v>103</v>
-      </c>
-      <c r="D27" s="236"/>
-      <c r="E27" s="236"/>
-      <c r="F27" s="237"/>
-    </row>
-    <row r="28" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="33"/>
-      <c r="B28" s="27">
+      <c r="C27" s="221" t="s">
+        <v>134</v>
+      </c>
+      <c r="D27" s="222"/>
+      <c r="E27" s="222"/>
+      <c r="F27" s="223"/>
+      <c r="G27" s="101" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="36"/>
+      <c r="B28" s="28">
         <v>5</v>
       </c>
-      <c r="C28" s="204" t="s">
-        <v>104</v>
-      </c>
-      <c r="D28" s="205"/>
-      <c r="E28" s="205"/>
-      <c r="F28" s="206"/>
-    </row>
-    <row r="29" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="34"/>
-      <c r="B29" s="29">
+      <c r="C28" s="241" t="s">
+        <v>135</v>
+      </c>
+      <c r="D28" s="242"/>
+      <c r="E28" s="242"/>
+      <c r="F28" s="243"/>
+      <c r="G28" s="101" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="37"/>
+      <c r="B29" s="30">
         <v>6</v>
       </c>
-      <c r="C29" s="231" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" s="232"/>
-      <c r="E29" s="233"/>
-      <c r="F29" s="234"/>
-    </row>
-    <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="31">
+      <c r="C29" s="253" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" s="254"/>
+      <c r="E29" s="255"/>
+      <c r="F29" s="256"/>
+      <c r="G29" s="101" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="55" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="33">
         <v>1</v>
       </c>
-      <c r="C30" s="219"/>
-      <c r="D30" s="220"/>
-      <c r="E30" s="220"/>
-      <c r="F30" s="221"/>
-    </row>
-    <row r="31" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="47"/>
-      <c r="B31" s="27">
+      <c r="C30" s="238"/>
+      <c r="D30" s="239"/>
+      <c r="E30" s="239"/>
+      <c r="F30" s="240"/>
+      <c r="G30" s="54"/>
+    </row>
+    <row r="31" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="51"/>
+      <c r="B31" s="28">
         <v>2</v>
       </c>
-      <c r="C31" s="204" t="s">
-        <v>106</v>
-      </c>
-      <c r="D31" s="205"/>
-      <c r="E31" s="205"/>
-      <c r="F31" s="206"/>
-    </row>
-    <row r="32" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="47"/>
-      <c r="B32" s="27">
+      <c r="C31" s="241" t="s">
+        <v>137</v>
+      </c>
+      <c r="D31" s="242"/>
+      <c r="E31" s="242"/>
+      <c r="F31" s="243"/>
+      <c r="G31" s="101" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="51"/>
+      <c r="B32" s="28">
         <v>3</v>
       </c>
-      <c r="C32" s="204" t="s">
-        <v>107</v>
-      </c>
-      <c r="D32" s="205"/>
-      <c r="E32" s="205"/>
-      <c r="F32" s="206"/>
-    </row>
-    <row r="33" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="45"/>
-      <c r="B33" s="29">
+      <c r="C32" s="241" t="s">
+        <v>138</v>
+      </c>
+      <c r="D32" s="242"/>
+      <c r="E32" s="242"/>
+      <c r="F32" s="243"/>
+      <c r="G32" s="101" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="49"/>
+      <c r="B33" s="30">
         <v>4</v>
       </c>
-      <c r="C33" s="228"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="230"/>
-    </row>
-    <row r="34" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="57"/>
-      <c r="B34" s="58"/>
-      <c r="C34" s="222"/>
-      <c r="D34" s="223"/>
-      <c r="E34" s="223"/>
-      <c r="F34" s="224"/>
-    </row>
-    <row r="35" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="40"/>
-      <c r="B35" s="59" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="225" t="s">
-        <v>56</v>
-      </c>
-      <c r="D35" s="226"/>
-      <c r="E35" s="226"/>
-      <c r="F35" s="227"/>
-    </row>
-    <row r="36" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="60" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" s="61"/>
-      <c r="C36" s="166" t="s">
-        <v>45</v>
-      </c>
-      <c r="D36" s="166"/>
-      <c r="E36" s="166"/>
-      <c r="F36" s="166"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C33" s="250"/>
+      <c r="D33" s="251"/>
+      <c r="E33" s="251"/>
+      <c r="F33" s="252"/>
+      <c r="G33" s="102"/>
+    </row>
+    <row r="34" spans="1:7" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="62"/>
+      <c r="B34" s="63"/>
+      <c r="C34" s="244"/>
+      <c r="D34" s="245"/>
+      <c r="E34" s="245"/>
+      <c r="F34" s="246"/>
+      <c r="G34" s="65"/>
+    </row>
+    <row r="35" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="44"/>
+      <c r="B35" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="247" t="s">
+        <v>67</v>
+      </c>
+      <c r="D35" s="248"/>
+      <c r="E35" s="248"/>
+      <c r="F35" s="249"/>
+      <c r="G35" s="100" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="67" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="68"/>
+      <c r="C36" s="179" t="s">
+        <v>54</v>
+      </c>
+      <c r="D36" s="179"/>
+      <c r="E36" s="179"/>
+      <c r="F36" s="179"/>
+      <c r="G36" s="69"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C26:F26"/>
@@ -3914,6 +4282,25 @@
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="E18:F18"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
   </mergeCells>
   <conditionalFormatting sqref="C8">
     <cfRule type="expression" priority="1">
@@ -3936,7 +4323,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3945,78 +4332,79 @@
     <col min="4" max="4" width="20.85546875" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.5703125" style="2" customWidth="1"/>
     <col min="6" max="6" width="21.85546875" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A1" s="64" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="66" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="75" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" s="64" t="s">
-        <v>60</v>
-      </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="66" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A2" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="75" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="66" t="s">
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="75" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="67" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F4" s="76" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -4026,35 +4414,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="249" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="297" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="249"/>
-      <c r="E7" s="46" t="s">
-        <v>29</v>
+      <c r="D7" s="297"/>
+      <c r="E7" s="50" t="s">
+        <v>30</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="203" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" s="203"/>
-      <c r="E8" s="203"/>
-      <c r="F8" s="203"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+      <c r="C8" s="272" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" s="272"/>
+      <c r="E8" s="272"/>
+      <c r="F8" s="272"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>0</v>
@@ -4065,340 +4453,388 @@
       <c r="D9" s="21"/>
       <c r="E9" s="22"/>
       <c r="F9" s="23"/>
-    </row>
-    <row r="10" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="25">
+      <c r="G9" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="26">
         <v>2</v>
       </c>
-      <c r="C10" s="253"/>
-      <c r="D10" s="254"/>
-      <c r="E10" s="254"/>
-      <c r="F10" s="255"/>
-    </row>
-    <row r="11" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="26"/>
-      <c r="B11" s="27">
+      <c r="C10" s="301"/>
+      <c r="D10" s="302"/>
+      <c r="E10" s="302"/>
+      <c r="F10" s="303"/>
+      <c r="G10" s="34"/>
+    </row>
+    <row r="11" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="27"/>
+      <c r="B11" s="28">
         <v>3</v>
       </c>
-      <c r="C11" s="101" t="s">
-        <v>116</v>
-      </c>
-      <c r="D11" s="147"/>
-      <c r="E11" s="147"/>
-      <c r="F11" s="104"/>
-    </row>
-    <row r="12" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="26"/>
-      <c r="B12" s="27">
+      <c r="C11" s="167" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" s="208"/>
+      <c r="E11" s="208"/>
+      <c r="F11" s="170"/>
+      <c r="G11" s="98" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="27"/>
+      <c r="B12" s="28">
         <v>4</v>
       </c>
-      <c r="C12" s="141" t="s">
-        <v>111</v>
-      </c>
-      <c r="D12" s="142"/>
-      <c r="E12" s="142"/>
-      <c r="F12" s="165"/>
-    </row>
-    <row r="13" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="28"/>
-      <c r="B13" s="29">
+      <c r="C12" s="220" t="s">
+        <v>142</v>
+      </c>
+      <c r="D12" s="177"/>
+      <c r="E12" s="177"/>
+      <c r="F12" s="178"/>
+      <c r="G12" s="98" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="29"/>
+      <c r="B13" s="30">
         <v>5</v>
       </c>
-      <c r="C13" s="259" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" s="260"/>
-      <c r="E13" s="260"/>
-      <c r="F13" s="261"/>
-    </row>
-    <row r="14" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="31">
+      <c r="C13" s="306" t="s">
+        <v>141</v>
+      </c>
+      <c r="D13" s="307"/>
+      <c r="E13" s="307"/>
+      <c r="F13" s="308"/>
+      <c r="G13" s="98" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="33">
         <v>3</v>
       </c>
-      <c r="C14" s="250"/>
-      <c r="D14" s="251"/>
-      <c r="E14" s="251"/>
-      <c r="F14" s="252"/>
-    </row>
-    <row r="15" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27">
+      <c r="C14" s="298"/>
+      <c r="D14" s="299"/>
+      <c r="E14" s="299"/>
+      <c r="F14" s="300"/>
+      <c r="G14" s="34"/>
+    </row>
+    <row r="15" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="27"/>
+      <c r="B15" s="28">
         <v>4</v>
       </c>
-      <c r="C15" s="75" t="s">
-        <v>112</v>
-      </c>
-      <c r="D15" s="76"/>
-      <c r="E15" s="76"/>
-      <c r="F15" s="77"/>
-    </row>
-    <row r="16" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27">
+      <c r="C15" s="122" t="s">
+        <v>143</v>
+      </c>
+      <c r="D15" s="123"/>
+      <c r="E15" s="123"/>
+      <c r="F15" s="124"/>
+      <c r="G15" s="94" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="27"/>
+      <c r="B16" s="28">
         <v>5</v>
       </c>
-      <c r="C16" s="101" t="s">
-        <v>125</v>
-      </c>
-      <c r="D16" s="147"/>
-      <c r="E16" s="147"/>
-      <c r="F16" s="104"/>
-    </row>
-    <row r="17" spans="1:6" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="32"/>
-      <c r="B17" s="29">
+      <c r="C16" s="167" t="s">
+        <v>159</v>
+      </c>
+      <c r="D16" s="208"/>
+      <c r="E16" s="208"/>
+      <c r="F16" s="170"/>
+      <c r="G16" s="94" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="35"/>
+      <c r="B17" s="30">
         <v>6</v>
       </c>
-      <c r="C17" s="170" t="s">
-        <v>125</v>
-      </c>
-      <c r="D17" s="171"/>
-      <c r="E17" s="171"/>
-      <c r="F17" s="172"/>
-    </row>
-    <row r="18" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="31">
+      <c r="C17" s="186" t="s">
+        <v>159</v>
+      </c>
+      <c r="D17" s="187"/>
+      <c r="E17" s="187"/>
+      <c r="F17" s="188"/>
+      <c r="G17" s="105" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="33">
         <v>2</v>
       </c>
-      <c r="C18" s="256" t="s">
-        <v>115</v>
-      </c>
-      <c r="D18" s="257"/>
-      <c r="E18" s="257"/>
-      <c r="F18" s="258"/>
-    </row>
-    <row r="19" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27">
+      <c r="C18" s="304" t="s">
+        <v>146</v>
+      </c>
+      <c r="D18" s="305"/>
+      <c r="E18" s="305"/>
+      <c r="F18" s="295"/>
+      <c r="G18" s="99" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="27"/>
+      <c r="B19" s="28">
         <v>3</v>
       </c>
-      <c r="C19" s="156" t="s">
-        <v>115</v>
-      </c>
-      <c r="D19" s="157"/>
-      <c r="E19" s="157"/>
-      <c r="F19" s="158"/>
-    </row>
-    <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27">
+      <c r="C19" s="217" t="s">
+        <v>146</v>
+      </c>
+      <c r="D19" s="218"/>
+      <c r="E19" s="218"/>
+      <c r="F19" s="219"/>
+      <c r="G19" s="94" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="27"/>
+      <c r="B20" s="28">
         <v>5</v>
       </c>
-      <c r="C20" s="101" t="s">
-        <v>113</v>
-      </c>
-      <c r="D20" s="147"/>
-      <c r="E20" s="147"/>
-      <c r="F20" s="104"/>
-    </row>
-    <row r="21" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="32"/>
-      <c r="B21" s="29">
+      <c r="C20" s="167" t="s">
+        <v>144</v>
+      </c>
+      <c r="D20" s="208"/>
+      <c r="E20" s="208"/>
+      <c r="F20" s="170"/>
+      <c r="G20" s="94" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="35"/>
+      <c r="B21" s="30">
         <v>6</v>
       </c>
-      <c r="C21" s="148" t="s">
-        <v>114</v>
-      </c>
-      <c r="D21" s="149"/>
-      <c r="E21" s="149"/>
-      <c r="F21" s="150"/>
-    </row>
-    <row r="22" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="31">
+      <c r="C21" s="209" t="s">
+        <v>145</v>
+      </c>
+      <c r="D21" s="210"/>
+      <c r="E21" s="210"/>
+      <c r="F21" s="211"/>
+      <c r="G21" s="87" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="33">
         <v>3</v>
       </c>
-      <c r="C22" s="250"/>
-      <c r="D22" s="251"/>
-      <c r="E22" s="251"/>
-      <c r="F22" s="252"/>
-    </row>
-    <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="26"/>
-      <c r="B23" s="27">
+      <c r="C22" s="298"/>
+      <c r="D22" s="299"/>
+      <c r="E22" s="299"/>
+      <c r="F22" s="300"/>
+      <c r="G22" s="82"/>
+    </row>
+    <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="27"/>
+      <c r="B23" s="28">
         <v>4</v>
       </c>
-      <c r="C23" s="84"/>
-      <c r="D23" s="85"/>
-      <c r="E23" s="85"/>
-      <c r="F23" s="86"/>
-    </row>
-    <row r="24" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="26"/>
-      <c r="B24" s="27">
+      <c r="C23" s="150"/>
+      <c r="D23" s="151"/>
+      <c r="E23" s="151"/>
+      <c r="F23" s="152"/>
+      <c r="G23" s="80"/>
+    </row>
+    <row r="24" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="27"/>
+      <c r="B24" s="28">
         <v>5</v>
       </c>
-      <c r="C24" s="101" t="s">
-        <v>113</v>
-      </c>
-      <c r="D24" s="147"/>
-      <c r="E24" s="147"/>
-      <c r="F24" s="104"/>
-    </row>
-    <row r="25" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="32"/>
-      <c r="B25" s="29">
+      <c r="C24" s="167" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" s="208"/>
+      <c r="E24" s="208"/>
+      <c r="F24" s="170"/>
+      <c r="G24" s="94" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="35"/>
+      <c r="B25" s="30">
         <v>6</v>
       </c>
-      <c r="C25" s="170" t="s">
-        <v>114</v>
-      </c>
-      <c r="D25" s="171"/>
-      <c r="E25" s="171"/>
-      <c r="F25" s="172"/>
-    </row>
-    <row r="26" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="31">
+      <c r="C25" s="186" t="s">
+        <v>145</v>
+      </c>
+      <c r="D25" s="187"/>
+      <c r="E25" s="187"/>
+      <c r="F25" s="188"/>
+      <c r="G25" s="94" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="33">
         <v>2</v>
       </c>
-      <c r="C26" s="273"/>
-      <c r="D26" s="274"/>
-      <c r="E26" s="274" t="s">
+      <c r="C26" s="282"/>
+      <c r="D26" s="283"/>
+      <c r="E26" s="283" t="s">
+        <v>84</v>
+      </c>
+      <c r="F26" s="284"/>
+      <c r="G26" s="86" t="s">
         <v>70</v>
       </c>
-      <c r="F26" s="275"/>
-    </row>
-    <row r="27" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="33"/>
-      <c r="B27" s="27">
+    </row>
+    <row r="27" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="36"/>
+      <c r="B27" s="28">
         <v>3</v>
       </c>
-      <c r="C27" s="115"/>
-      <c r="D27" s="116"/>
-      <c r="E27" s="116" t="s">
+      <c r="C27" s="116"/>
+      <c r="D27" s="117"/>
+      <c r="E27" s="117" t="s">
+        <v>84</v>
+      </c>
+      <c r="F27" s="118"/>
+      <c r="G27" s="98" t="s">
         <v>70</v>
       </c>
-      <c r="F27" s="117"/>
-    </row>
-    <row r="28" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="33"/>
-      <c r="B28" s="27">
+    </row>
+    <row r="28" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="36"/>
+      <c r="B28" s="28">
         <v>4</v>
       </c>
-      <c r="C28" s="115" t="s">
-        <v>71</v>
-      </c>
-      <c r="D28" s="116"/>
-      <c r="E28" s="116"/>
-      <c r="F28" s="117"/>
-    </row>
-    <row r="29" spans="1:6" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="34"/>
-      <c r="B29" s="29">
+      <c r="C28" s="116" t="s">
+        <v>85</v>
+      </c>
+      <c r="D28" s="117"/>
+      <c r="E28" s="117"/>
+      <c r="F28" s="118"/>
+      <c r="G28" s="98" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="37"/>
+      <c r="B29" s="30">
         <v>5</v>
       </c>
-      <c r="C29" s="266" t="s">
-        <v>71</v>
-      </c>
-      <c r="D29" s="267"/>
-      <c r="E29" s="268"/>
-      <c r="F29" s="269"/>
-    </row>
-    <row r="30" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="25">
+      <c r="C29" s="289" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" s="290"/>
+      <c r="E29" s="291"/>
+      <c r="F29" s="292"/>
+      <c r="G29" s="84" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="26">
         <v>1</v>
       </c>
-      <c r="C30" s="138"/>
-      <c r="D30" s="270"/>
-      <c r="E30" s="271" t="s">
-        <v>119</v>
-      </c>
-      <c r="F30" s="258"/>
-    </row>
-    <row r="31" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="47"/>
-      <c r="B31" s="25">
+      <c r="C30" s="180"/>
+      <c r="D30" s="293"/>
+      <c r="E30" s="294" t="s">
+        <v>153</v>
+      </c>
+      <c r="F30" s="295"/>
+      <c r="G30" s="93" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="51"/>
+      <c r="B31" s="26">
         <v>2</v>
       </c>
-      <c r="C31" s="115" t="s">
-        <v>117</v>
-      </c>
-      <c r="D31" s="116"/>
-      <c r="E31" s="116" t="s">
-        <v>119</v>
-      </c>
-      <c r="F31" s="117"/>
-    </row>
-    <row r="32" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="36"/>
-      <c r="B32" s="62">
+      <c r="C31" s="116" t="s">
+        <v>151</v>
+      </c>
+      <c r="D31" s="117"/>
+      <c r="E31" s="117" t="s">
+        <v>153</v>
+      </c>
+      <c r="F31" s="118"/>
+      <c r="G31" s="93" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="39"/>
+      <c r="B32" s="70">
         <v>3</v>
       </c>
-      <c r="C32" s="75" t="s">
-        <v>120</v>
-      </c>
-      <c r="D32" s="272"/>
-      <c r="E32" s="97" t="s">
-        <v>118</v>
-      </c>
-      <c r="F32" s="77"/>
-    </row>
-    <row r="33" spans="1:6" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="48"/>
-      <c r="B33" s="49">
+      <c r="C32" s="122" t="s">
+        <v>154</v>
+      </c>
+      <c r="D32" s="296"/>
+      <c r="E32" s="163" t="s">
+        <v>152</v>
+      </c>
+      <c r="F32" s="124"/>
+      <c r="G32" s="97" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="52"/>
+      <c r="B33" s="53">
         <v>4</v>
       </c>
-      <c r="C33" s="262" t="s">
-        <v>120</v>
-      </c>
-      <c r="D33" s="263"/>
-      <c r="E33" s="264"/>
-      <c r="F33" s="265"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C33" s="285" t="s">
+        <v>154</v>
+      </c>
+      <c r="D33" s="286"/>
+      <c r="E33" s="287"/>
+      <c r="F33" s="288"/>
+      <c r="G33" s="84" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A34" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="C31:D31"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C15:F15"/>
@@ -4414,6 +4850,25 @@
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="C24:F24"/>
   </mergeCells>
   <conditionalFormatting sqref="C8">
     <cfRule type="expression" priority="1">
